--- a/1. RAG/data/4_testing/range_of_k/RAG_eval_k=15.xlsx
+++ b/1. RAG/data/4_testing/range_of_k/RAG_eval_k=15.xlsx
@@ -548,35 +548,35 @@
       </c>
       <c r="C2" s="3" t="inlineStr">
         <is>
-          <t>I don't have enough information to answer that.</t>
+          <t>According to the context provided, 2% of gay men in Germany reported feeling discriminated against in the past year when showing their ID or any official document that identifies their sex.</t>
         </is>
       </c>
       <c r="D2" s="2" t="n">
         <v>15</v>
       </c>
       <c r="E2" s="2" t="n">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="F2" s="2" t="n">
-        <v>0.733</v>
+        <v>0.867</v>
       </c>
       <c r="G2" s="2" t="n">
-        <v>0.7063</v>
+        <v>0.7155</v>
       </c>
       <c r="H2" s="2" t="n">
-        <v>8</v>
+        <v>31</v>
       </c>
       <c r="I2" s="2" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="J2" s="2" t="n">
-        <v>0.333</v>
+        <v>0.667</v>
       </c>
       <c r="K2" s="2" t="n">
-        <v>0</v>
+        <v>0.667</v>
       </c>
       <c r="L2" s="2" t="n">
-        <v>61.2</v>
+        <v>25.3</v>
       </c>
     </row>
     <row r="3">
@@ -590,7 +590,7 @@
       </c>
       <c r="C3" s="5" t="inlineStr">
         <is>
-          <t>Lesbian women in France feel somewhat comfortable being open about their identity at work, with 18% stating they are always open, 54% saying they are selectively open, and 28% indicating they hide their LGBT identity.</t>
+          <t>According to the provided context, lesbian women in France feel the following about being open about their identity at work: 18% are always open, 54% are selectively open, and 28% hide their LGBT identity. This indicates that a majority (54%) prefer to be selectively open rather than fully open or completely hidden.</t>
         </is>
       </c>
       <c r="D3" s="4" t="n">
@@ -603,22 +603,22 @@
         <v>0.8</v>
       </c>
       <c r="G3" s="4" t="n">
-        <v>0.6788</v>
+        <v>0.6816</v>
       </c>
       <c r="H3" s="4" t="n">
-        <v>35</v>
+        <v>52</v>
       </c>
       <c r="I3" s="4" t="b">
         <v>1</v>
       </c>
       <c r="J3" s="4" t="n">
-        <v>0.48</v>
+        <v>0.351</v>
       </c>
       <c r="K3" s="4" t="n">
-        <v>0.867</v>
+        <v>0.8</v>
       </c>
       <c r="L3" s="4" t="n">
-        <v>21.4</v>
+        <v>27.5</v>
       </c>
     </row>
     <row r="4">
@@ -639,13 +639,13 @@
         <v>15</v>
       </c>
       <c r="E4" s="2" t="n">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="F4" s="2" t="n">
-        <v>0.8</v>
+        <v>0.867</v>
       </c>
       <c r="G4" s="2" t="n">
-        <v>0.7003</v>
+        <v>0.6655</v>
       </c>
       <c r="H4" s="2" t="n">
         <v>8</v>
@@ -684,10 +684,10 @@
         <v>3</v>
       </c>
       <c r="F5" s="4" t="n">
-        <v>0.8</v>
+        <v>0.867</v>
       </c>
       <c r="G5" s="4" t="n">
-        <v>0.6603</v>
+        <v>0.6616</v>
       </c>
       <c r="H5" s="4" t="n">
         <v>8</v>
@@ -726,10 +726,10 @@
         <v>2</v>
       </c>
       <c r="F6" s="2" t="n">
-        <v>0.8</v>
+        <v>0.867</v>
       </c>
       <c r="G6" s="2" t="n">
-        <v>0.5735</v>
+        <v>0.5775</v>
       </c>
       <c r="H6" s="2" t="n">
         <v>8</v>
@@ -765,13 +765,13 @@
         <v>15</v>
       </c>
       <c r="E7" s="4" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="F7" s="4" t="n">
-        <v>0.8</v>
+        <v>0.867</v>
       </c>
       <c r="G7" s="4" t="n">
-        <v>0.5425</v>
+        <v>0.5495</v>
       </c>
       <c r="H7" s="4" t="n">
         <v>8</v>
@@ -810,10 +810,10 @@
         <v>3</v>
       </c>
       <c r="F8" s="2" t="n">
-        <v>0.8</v>
+        <v>0.867</v>
       </c>
       <c r="G8" s="2" t="n">
-        <v>0.512</v>
+        <v>0.5162</v>
       </c>
       <c r="H8" s="2" t="n">
         <v>8</v>
@@ -852,10 +852,10 @@
         <v>3</v>
       </c>
       <c r="F9" s="4" t="n">
-        <v>0.8</v>
+        <v>0.867</v>
       </c>
       <c r="G9" s="4" t="n">
-        <v>0.6075</v>
+        <v>0.3607</v>
       </c>
       <c r="H9" s="4" t="n">
         <v>8</v>
@@ -864,7 +864,7 @@
         <v>0</v>
       </c>
       <c r="J9" s="4" t="n">
-        <v>0</v>
+        <v>0.333</v>
       </c>
       <c r="K9" s="4" t="n">
         <v>0.182</v>
@@ -941,7 +941,7 @@
       </c>
       <c r="D2" s="3" t="inlineStr">
         <is>
-          <t>C:\Users\RAZER\Desktop\portfolio-projects\1. RAG\data\3_txt_KB\LGBT_EU\by_country\LGBT_Survey_Discrimination\c2a_b_answer_by_Germany.txt</t>
+          <t>C:\Users\RAZER\Desktop\portfolio-projects\1. RAG\data\3_txt_KB\LGBT_EU\by_subset\LGBT_Survey_Discrimination\c4_k_answer_by_Gay.txt</t>
         </is>
       </c>
       <c r="E2" s="2" t="b">
@@ -949,7 +949,7 @@
       </c>
       <c r="F2" s="3" t="inlineStr">
         <is>
-          <t>Question c2a_b — In the last 12 months, in the country where you live, have you personally felt discriminated against or harassed because of being perceived as Gay? | Germany responses (Transgender): Yes: 39%, No: 55%, Don`t know: 6%</t>
+          <t>Question c4_k — During the last 12 months, have you personally felt discriminated against because of being L, G, B or T when showing your ID or any official document that identifies your sex? | Gay responses in Germany: Yes: 2%, No: 96%, Don`t know: 1%</t>
         </is>
       </c>
     </row>
@@ -965,17 +965,13 @@
       <c r="C3" s="4" t="n">
         <v>2</v>
       </c>
-      <c r="D3" s="5" t="inlineStr">
-        <is>
-          <t>C:\Users\RAZER\Desktop\portfolio-projects\1. RAG\data\3_txt_KB\LGBT_EU\by_country\LGBT_Survey_Discrimination\c2a_c_answer_by_Germany.txt</t>
-        </is>
-      </c>
+      <c r="D3" s="5" t="inlineStr"/>
       <c r="E3" s="4" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="F3" s="5" t="inlineStr">
         <is>
-          <t>Question c2a_c — In the last 12 months, in the country where you live, have you personally felt discriminated against or harassed because of being perceived as Bisexual? | Germany responses (Transgender): Yes: 19%, No: 73%, Don`t know: 8%</t>
+          <t>Question c4_k — During the last 12 months, have you personally felt discriminated against because of being L, G, B or T when showing your ID or any official document that identifies your sex? | Gay responses in Germany: Yes: 2%, No: 96%, Don`t know: 1%</t>
         </is>
       </c>
     </row>
@@ -991,17 +987,13 @@
       <c r="C4" s="2" t="n">
         <v>3</v>
       </c>
-      <c r="D4" s="3" t="inlineStr">
-        <is>
-          <t>C:\Users\RAZER\Desktop\portfolio-projects\1. RAG\data\3_txt_KB\LGBT_EU\by_country\LGBT_Survey_Discrimination\c2a_c_answer_by_Germany.txt</t>
-        </is>
-      </c>
+      <c r="D4" s="3" t="inlineStr"/>
       <c r="E4" s="2" t="b">
         <v>1</v>
       </c>
       <c r="F4" s="3" t="inlineStr">
         <is>
-          <t>Question c2a_c — In the last 12 months, in the country where you live, have you personally felt discriminated against or harassed because of being perceived as Bisexual? | Germany responses (Transgender): Yes: 19%, No: 73%, Don`t know: 8%</t>
+          <t>Question c4_k — During the last 12 months, have you personally felt discriminated against because of being L, G, B or T when showing your ID or any official document that identifies your sex? | Gay responses in Germany: Yes: 2%, No: 96%, Don`t know: 1%</t>
         </is>
       </c>
     </row>
@@ -1019,11 +1011,11 @@
       </c>
       <c r="D5" s="5" t="inlineStr"/>
       <c r="E5" s="4" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="F5" s="5" t="inlineStr">
         <is>
-          <t>Question c8a_e — During your employment in the last 5 years, have you experienced a general negative attitude at work against people because they are lesbian, gay, bisexual and/or transgender? | Germany responses (Bisexual men): Always: 4%, Often: 23%, Rarely: 41%, Never: 32%</t>
+          <t>Question c4_k — During the last 12 months, have you personally felt discriminated against because of being L, G, B or T when showing your ID or any official document that identifies your sex? | Gay responses in Germany: Yes: 2%, No: 96%, Don`t know: 1%</t>
         </is>
       </c>
     </row>
@@ -1039,13 +1031,17 @@
       <c r="C6" s="2" t="n">
         <v>5</v>
       </c>
-      <c r="D6" s="3" t="inlineStr"/>
+      <c r="D6" s="3" t="inlineStr">
+        <is>
+          <t>C:\Users\RAZER\Desktop\portfolio-projects\1. RAG\data\3_txt_KB\LGBT_EU\by_subset\LGBT_Survey_Discrimination\c4_k_answer_by_Gay.txt</t>
+        </is>
+      </c>
       <c r="E6" s="2" t="b">
         <v>1</v>
       </c>
       <c r="F6" s="3" t="inlineStr">
         <is>
-          <t>Question c8a_e — During your employment in the last 5 years, have you experienced a general negative attitude at work against people because they are lesbian, gay, bisexual and/or transgender? | Germany responses (Bisexual men): Always: 4%, Often: 23%, Rarely: 41%, Never: 32%</t>
+          <t>Question c4_k — During the last 12 months, have you personally felt discriminated against because of being L, G, B or T when showing your ID or any official document that identifies your sex? | Gay responses in Germany: Yes: 2%, No: 96%, Don`t know: 1%</t>
         </is>
       </c>
     </row>
@@ -1061,13 +1057,17 @@
       <c r="C7" s="4" t="n">
         <v>6</v>
       </c>
-      <c r="D7" s="5" t="inlineStr"/>
+      <c r="D7" s="5" t="inlineStr">
+        <is>
+          <t>C:\Users\RAZER\Desktop\portfolio-projects\1. RAG\data\3_txt_KB\LGBT_EU\by_subset\LGBT_Survey_Discrimination\c4_k_answer_by_Gay.txt</t>
+        </is>
+      </c>
       <c r="E7" s="4" t="b">
         <v>1</v>
       </c>
       <c r="F7" s="5" t="inlineStr">
         <is>
-          <t>Question c8a_e — During your employment in the last 5 years, have you experienced a general negative attitude at work against people because they are lesbian, gay, bisexual and/or transgender? | Germany responses (Bisexual men): Always: 4%, Often: 23%, Rarely: 41%, Never: 32%</t>
+          <t>Question c4_k — During the last 12 months, have you personally felt discriminated against because of being L, G, B or T when showing your ID or any official document that identifies your sex? | Gay responses in Germany: Yes: 2%, No: 96%, Don`t know: 1%</t>
         </is>
       </c>
     </row>
@@ -1085,7 +1085,7 @@
       </c>
       <c r="D8" s="3" t="inlineStr">
         <is>
-          <t>C:\Users\RAZER\Desktop\portfolio-projects\1. RAG\data\3_txt_KB\LGBT_EU\by_country\LGBT_Survey_Discrimination\c8a_e_answer_by_Germany.txt</t>
+          <t>C:\Users\RAZER\Desktop\portfolio-projects\1. RAG\data\3_txt_KB\LGBT_EU\by_subset\LGBT_Survey_Discrimination\c4_k_answer_by_Gay.txt</t>
         </is>
       </c>
       <c r="E8" s="2" t="b">
@@ -1093,7 +1093,7 @@
       </c>
       <c r="F8" s="3" t="inlineStr">
         <is>
-          <t>Question c8a_e — During your employment in the last 5 years, have you experienced a general negative attitude at work against people because they are lesbian, gay, bisexual and/or transgender? | Germany responses (Bisexual men): Always: 4%, Often: 23%, Rarely: 41%, Never: 32%</t>
+          <t>Question c4_k — During the last 12 months, have you personally felt discriminated against because of being L, G, B or T when showing your ID or any official document that identifies your sex? | Gay responses in Germany: Yes: 2%, No: 96%, Don`t know: 1%</t>
         </is>
       </c>
     </row>
@@ -1111,7 +1111,7 @@
       </c>
       <c r="D9" s="5" t="inlineStr">
         <is>
-          <t>C:\Users\RAZER\Desktop\portfolio-projects\1. RAG\data\3_txt_KB\LGBT_EU\by_country\LGBT_Survey_Discrimination\c8a_e_answer_by_Germany.txt</t>
+          <t>C:\Users\RAZER\Desktop\portfolio-projects\1. RAG\data\3_txt_KB\LGBT_EU\by_subset\LGBT_Survey_Discrimination\c4_k_answer_by_Gay.txt</t>
         </is>
       </c>
       <c r="E9" s="4" t="b">
@@ -1119,7 +1119,7 @@
       </c>
       <c r="F9" s="5" t="inlineStr">
         <is>
-          <t>Question c8a_e — During your employment in the last 5 years, have you experienced a general negative attitude at work against people because they are lesbian, gay, bisexual and/or transgender? | Germany responses (Bisexual men): Always: 4%, Often: 23%, Rarely: 41%, Never: 32%</t>
+          <t>Question c4_k — During the last 12 months, have you personally felt discriminated against because of being L, G, B or T when showing your ID or any official document that identifies your sex? | Gay responses in Germany: Yes: 2%, No: 96%, Don`t know: 1%</t>
         </is>
       </c>
     </row>
@@ -1137,7 +1137,7 @@
       </c>
       <c r="D10" s="3" t="inlineStr">
         <is>
-          <t>C:\Users\RAZER\Desktop\portfolio-projects\1. RAG\data\3_txt_KB\LGBT_EU\by_country\LGBT_Survey_Discrimination\c8a_e_answer_by_Germany.txt</t>
+          <t>C:\Users\RAZER\Desktop\portfolio-projects\1. RAG\data\3_txt_KB\LGBT_EU\by_subset\LGBT_Survey_Discrimination\c4_k_answer_by_Gay.txt</t>
         </is>
       </c>
       <c r="E10" s="2" t="b">
@@ -1145,7 +1145,7 @@
       </c>
       <c r="F10" s="3" t="inlineStr">
         <is>
-          <t>Question c8a_e — During your employment in the last 5 years, have you experienced a general negative attitude at work against people because they are lesbian, gay, bisexual and/or transgender? | Germany responses (Bisexual men): Always: 4%, Often: 23%, Rarely: 41%, Never: 32%</t>
+          <t>Question c4_k — During the last 12 months, have you personally felt discriminated against because of being L, G, B or T when showing your ID or any official document that identifies your sex? | Gay responses in Germany: Yes: 2%, No: 96%, Don`t know: 1%</t>
         </is>
       </c>
     </row>
@@ -1163,7 +1163,7 @@
       </c>
       <c r="D11" s="5" t="inlineStr">
         <is>
-          <t>C:\Users\RAZER\Desktop\portfolio-projects\1. RAG\data\3_txt_KB\LGBT_EU\by_country\LGBT_Survey_Discrimination\c8a_e_answer_by_Germany.txt</t>
+          <t>C:\Users\RAZER\Desktop\portfolio-projects\1. RAG\data\3_txt_KB\LGBT_EU\by_subset\LGBT_Survey_Discrimination\c4_k_answer_by_Gay.txt</t>
         </is>
       </c>
       <c r="E11" s="4" t="b">
@@ -1171,7 +1171,7 @@
       </c>
       <c r="F11" s="5" t="inlineStr">
         <is>
-          <t>Question c8a_e — During your employment in the last 5 years, have you experienced a general negative attitude at work against people because they are lesbian, gay, bisexual and/or transgender? | Germany responses (Bisexual men): Always: 4%, Often: 23%, Rarely: 41%, Never: 32%</t>
+          <t>Question c4_k — During the last 12 months, have you personally felt discriminated against because of being L, G, B or T when showing your ID or any official document that identifies your sex? | Gay responses in Germany: Yes: 2%, No: 96%, Don`t know: 1%</t>
         </is>
       </c>
     </row>
@@ -1187,13 +1187,17 @@
       <c r="C12" s="2" t="n">
         <v>11</v>
       </c>
-      <c r="D12" s="3" t="inlineStr"/>
+      <c r="D12" s="3" t="inlineStr">
+        <is>
+          <t>C:\Users\RAZER\Desktop\portfolio-projects\1. RAG\data\3_txt_KB\LGBT_EU\by_subset\LGBT_Survey_Discrimination\c4_k_answer_by_Gay.txt</t>
+        </is>
+      </c>
       <c r="E12" s="2" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="F12" s="3" t="inlineStr">
         <is>
-          <t>Question c8a_e — During your employment in the last 5 years, have you experienced a general negative attitude at work against people because they are lesbian, gay, bisexual and/or transgender? | Gay responses in Germany: Always: 3%, Often: 16%, Rarely: 40%, Never: 40%</t>
+          <t>Question c4_k — During the last 12 months, have you personally felt discriminated against because of being L, G, B or T when showing your ID or any official document that identifies your sex? | Gay responses in Germany: Yes: 2%, No: 96%, Don`t know: 1%</t>
         </is>
       </c>
     </row>
@@ -1209,13 +1213,17 @@
       <c r="C13" s="4" t="n">
         <v>12</v>
       </c>
-      <c r="D13" s="5" t="inlineStr"/>
+      <c r="D13" s="5" t="inlineStr">
+        <is>
+          <t>C:\Users\RAZER\Desktop\portfolio-projects\1. RAG\data\3_txt_KB\LGBT_EU\by_subset\LGBT_Survey_Discrimination\c4_k_answer_by_Bisexualmen.txt</t>
+        </is>
+      </c>
       <c r="E13" s="4" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="F13" s="5" t="inlineStr">
         <is>
-          <t>Question c8a_e — During your employment in the last 5 years, have you experienced a general negative attitude at work against people because they are lesbian, gay, bisexual and/or transgender? | Gay responses in Germany: Always: 3%, Often: 16%, Rarely: 40%, Never: 40%</t>
+          <t>Question c4_k — During the last 12 months, have you personally felt discriminated against because of being L, G, B or T when showing your ID or any official document that identifies your sex? | Bisexual men responses in Germany: Yes: 2%, No: 96%, Don`t know: 2%</t>
         </is>
       </c>
     </row>
@@ -1231,13 +1239,17 @@
       <c r="C14" s="2" t="n">
         <v>13</v>
       </c>
-      <c r="D14" s="3" t="inlineStr"/>
+      <c r="D14" s="3" t="inlineStr">
+        <is>
+          <t>C:\Users\RAZER\Desktop\portfolio-projects\1. RAG\data\3_txt_KB\LGBT_EU\by_subset\LGBT_Survey_Discrimination\c4_k_answer_by_Bisexualmen.txt</t>
+        </is>
+      </c>
       <c r="E14" s="2" t="b">
         <v>1</v>
       </c>
       <c r="F14" s="3" t="inlineStr">
         <is>
-          <t>Question c8a_e — During your employment in the last 5 years, have you experienced a general negative attitude at work against people because they are lesbian, gay, bisexual and/or transgender? | Gay responses in Germany: Always: 3%, Often: 16%, Rarely: 40%, Never: 40%</t>
+          <t>Question c4_k — During the last 12 months, have you personally felt discriminated against because of being L, G, B or T when showing your ID or any official document that identifies your sex? | Bisexual men responses in Germany: Yes: 2%, No: 96%, Don`t know: 2%</t>
         </is>
       </c>
     </row>
@@ -1253,17 +1265,13 @@
       <c r="C15" s="4" t="n">
         <v>14</v>
       </c>
-      <c r="D15" s="5" t="inlineStr">
-        <is>
-          <t>C:\Users\RAZER\Desktop\portfolio-projects\1. RAG\data\3_txt_KB\LGBT_EU\by_subset\LGBT_Survey_Discrimination\c8a_e_answer_by_Gay.txt</t>
-        </is>
-      </c>
+      <c r="D15" s="5" t="inlineStr"/>
       <c r="E15" s="4" t="b">
         <v>1</v>
       </c>
       <c r="F15" s="5" t="inlineStr">
         <is>
-          <t>Question c8a_e — During your employment in the last 5 years, have you experienced a general negative attitude at work against people because they are lesbian, gay, bisexual and/or transgender? | Gay responses in Germany: Always: 3%, Often: 16%, Rarely: 40%, Never: 40%</t>
+          <t>Question c4_k — During the last 12 months, have you personally felt discriminated against because of being L, G, B or T when showing your ID or any official document that identifies your sex? | Bisexual men responses in Germany: Yes: 2%, No: 96%, Don`t know: 2%</t>
         </is>
       </c>
     </row>
@@ -1281,7 +1289,7 @@
       </c>
       <c r="D16" s="3" t="inlineStr">
         <is>
-          <t>C:\Users\RAZER\Desktop\portfolio-projects\1. RAG\data\3_txt_KB\LGBT_EU\by_subset\LGBT_Survey_Discrimination\c8a_e_answer_by_Gay.txt</t>
+          <t>C:\Users\RAZER\Desktop\portfolio-projects\1. RAG\data\3_txt_KB\LGBT_EU\by_subset\LGBT_Survey_Discrimination\c4_k_answer_by_Bisexualmen.txt</t>
         </is>
       </c>
       <c r="E16" s="2" t="b">
@@ -1289,7 +1297,7 @@
       </c>
       <c r="F16" s="3" t="inlineStr">
         <is>
-          <t>Question c8a_e — During your employment in the last 5 years, have you experienced a general negative attitude at work against people because they are lesbian, gay, bisexual and/or transgender? | Gay responses in Germany: Always: 3%, Often: 16%, Rarely: 40%, Never: 40%</t>
+          <t>Question c4_k — During the last 12 months, have you personally felt discriminated against because of being L, G, B or T when showing your ID or any official document that identifies your sex? | Bisexual men responses in Germany: Yes: 2%, No: 96%, Don`t know: 2%</t>
         </is>
       </c>
     </row>
@@ -1482,14 +1490,18 @@
       <c r="C24" s="2" t="n">
         <v>8</v>
       </c>
-      <c r="D24" s="3" t="inlineStr"/>
+      <c r="D24" s="3" t="inlineStr">
+        <is>
+          <t>C:\Users\RAZER\Desktop\portfolio-projects\1. RAG\data\3_txt_KB\LGBT_EU\by_country\LGBT_Survey_DailyLife\open_at_work_answer_by_France.txt</t>
+        </is>
+      </c>
       <c r="E24" s="2" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="F24" s="3" t="inlineStr">
         <is>
-          <t>Question open_at_work — Have you been open about you being L, G, B or T? * | Bisexual women responses in France: Always open: 4%, selectively open: 49%, hide LGBT identity: 47%
-Question open_at_work — Have you been open about you being L, G, B or T? * | Bisexual women responses in Germany: Always open: 12%, selectively open: 62%, hide LGBT identity: 26%</t>
+          <t>Question open_at_work — Have you been open about you being L, G, B or T? * | France responses (Gay): Always open: 22%, selectively open: 49%, hide LGBT identity: 30%
+Question open_at_work — Have you been open about you being L, G, B or T? * | France responses (Lesbian): Always open: 18%, selectively open: 54%, hide LGBT identity: 28%</t>
         </is>
       </c>
     </row>
@@ -1505,14 +1517,18 @@
       <c r="C25" s="4" t="n">
         <v>9</v>
       </c>
-      <c r="D25" s="5" t="inlineStr"/>
+      <c r="D25" s="5" t="inlineStr">
+        <is>
+          <t>C:\Users\RAZER\Desktop\portfolio-projects\1. RAG\data\3_txt_KB\LGBT_EU\by_country\LGBT_Survey_DailyLife\open_at_work_answer_by_France.txt</t>
+        </is>
+      </c>
       <c r="E25" s="4" t="b">
         <v>1</v>
       </c>
       <c r="F25" s="5" t="inlineStr">
         <is>
-          <t>Question open_at_work — Have you been open about you being L, G, B or T? * | Bisexual women responses in France: Always open: 4%, selectively open: 49%, hide LGBT identity: 47%
-Question open_at_work — Have you been open about you being L, G, B or T? * | Bisexual women responses in Germany: Always open: 12%, selectively open: 62%, hide LGBT identity: 26%</t>
+          <t>Question open_at_work — Have you been open about you being L, G, B or T? * | France responses (Gay): Always open: 22%, selectively open: 49%, hide LGBT identity: 30%
+Question open_at_work — Have you been open about you being L, G, B or T? * | France responses (Lesbian): Always open: 18%, selectively open: 54%, hide LGBT identity: 28%</t>
         </is>
       </c>
     </row>
@@ -1528,14 +1544,18 @@
       <c r="C26" s="2" t="n">
         <v>10</v>
       </c>
-      <c r="D26" s="3" t="inlineStr"/>
+      <c r="D26" s="3" t="inlineStr">
+        <is>
+          <t>C:\Users\RAZER\Desktop\portfolio-projects\1. RAG\data\3_txt_KB\LGBT_EU\by_country\LGBT_Survey_DailyLife\open_at_work_answer_by_France.txt</t>
+        </is>
+      </c>
       <c r="E26" s="2" t="b">
         <v>1</v>
       </c>
       <c r="F26" s="3" t="inlineStr">
         <is>
-          <t>Question open_at_work — Have you been open about you being L, G, B or T? * | Bisexual women responses in France: Always open: 4%, selectively open: 49%, hide LGBT identity: 47%
-Question open_at_work — Have you been open about you being L, G, B or T? * | Bisexual women responses in Germany: Always open: 12%, selectively open: 62%, hide LGBT identity: 26%</t>
+          <t>Question open_at_work — Have you been open about you being L, G, B or T? * | France responses (Gay): Always open: 22%, selectively open: 49%, hide LGBT identity: 30%
+Question open_at_work — Have you been open about you being L, G, B or T? * | France responses (Lesbian): Always open: 18%, selectively open: 54%, hide LGBT identity: 28%</t>
         </is>
       </c>
     </row>
@@ -1553,7 +1573,7 @@
       </c>
       <c r="D27" s="5" t="inlineStr">
         <is>
-          <t>C:\Users\RAZER\Desktop\portfolio-projects\1. RAG\data\3_txt_KB\LGBT_EU\by_subset\LGBT_Survey_DailyLife\open_at_work_answer_by_Bisexualwomen.txt</t>
+          <t>C:\Users\RAZER\Desktop\portfolio-projects\1. RAG\data\3_txt_KB\LGBT_EU\by_country\LGBT_Survey_DailyLife\open_at_work_answer_by_France.txt</t>
         </is>
       </c>
       <c r="E27" s="4" t="b">
@@ -1561,8 +1581,8 @@
       </c>
       <c r="F27" s="5" t="inlineStr">
         <is>
-          <t>Question open_at_work — Have you been open about you being L, G, B or T? * | Bisexual women responses in France: Always open: 4%, selectively open: 49%, hide LGBT identity: 47%
-Question open_at_work — Have you been open about you being L, G, B or T? * | Bisexual women responses in Germany: Always open: 12%, selectively open: 62%, hide LGBT identity: 26%</t>
+          <t>Question open_at_work — Have you been open about you being L, G, B or T? * | France responses (Gay): Always open: 22%, selectively open: 49%, hide LGBT identity: 30%
+Question open_at_work — Have you been open about you being L, G, B or T? * | France responses (Lesbian): Always open: 18%, selectively open: 54%, hide LGBT identity: 28%</t>
         </is>
       </c>
     </row>
@@ -1580,16 +1600,18 @@
       </c>
       <c r="D28" s="3" t="inlineStr">
         <is>
-          <t>C:\Users\RAZER\Desktop\portfolio-projects\1. RAG\data\3_txt_KB\LGBT_EU\by_subset\LGBT_Survey_DailyLife\open_at_work_answer_by_Bisexualwomen.txt</t>
+          <t>C:\Users\RAZER\Desktop\portfolio-projects\1. RAG\data\3_txt_KB\LGBT_EU\by_country\LGBT_Survey_DailyLife\open_at_work_answer_by_France.txt</t>
         </is>
       </c>
       <c r="E28" s="2" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="F28" s="3" t="inlineStr">
         <is>
-          <t>Question open_at_work — Have you been open about you being L, G, B or T? * | Bisexual women responses in France: Always open: 4%, selectively open: 49%, hide LGBT identity: 47%
-Question open_at_work — Have you been open about you being L, G, B or T? * | Bisexual women responses in Germany: Always open: 12%, selectively open: 62%, hide LGBT identity: 26%</t>
+          <t>Question open_at_work — Have you been open about you being L, G, B or T? * | France responses (Bisexual men): Always open: 5%, selectively open: 37%, hide LGBT identity: 58%
+Question open_at_work — Have you been open about you being L, G, B or T? * | France responses (Bisexual women): Always open: 4%, selectively open: 49%, hide LGBT identity: 47%
+Question open_at_work — Have you been open about you being L, G, B or T? * | France responses (Gay): Always open: 22%, selectively open: 49%, hide LGBT identity: 30%
+Question open_at_work — Have you been open about you being L, G, B or T? * | France responses (Lesbian): Always open: 18%, selectively open: 54%, hide LGBT identity: 28%</t>
         </is>
       </c>
     </row>
@@ -1611,7 +1633,7 @@
         </is>
       </c>
       <c r="E29" s="4" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="F29" s="5" t="inlineStr">
         <is>
@@ -1661,16 +1683,16 @@
       </c>
       <c r="D31" s="5" t="inlineStr">
         <is>
-          <t>C:\Users\RAZER\Desktop\portfolio-projects\1. RAG\data\3_txt_KB\LGBT_EU\by_country\LGBT_Survey_DailyLife\open_at_work_answer_by_France.txt</t>
+          <t>C:\Users\RAZER\Desktop\portfolio-projects\1. RAG\data\3_txt_KB\LGBT_EU\by_subset\LGBT_Survey_DailyLife\open_at_work_answer_by_Bisexualwomen.txt</t>
         </is>
       </c>
       <c r="E31" s="4" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="F31" s="5" t="inlineStr">
         <is>
-          <t>Question open_at_work — Have you been open about you being L, G, B or T? * | France responses (Bisexual men): Always open: 5%, selectively open: 37%, hide LGBT identity: 58%
-Question open_at_work — Have you been open about you being L, G, B or T? * | France responses (Bisexual women): Always open: 4%, selectively open: 49%, hide LGBT identity: 47%</t>
+          <t>Question open_at_work — Have you been open about you being L, G, B or T? * | Bisexual women responses in France: Always open: 4%, selectively open: 49%, hide LGBT identity: 47%
+Question open_at_work — Have you been open about you being L, G, B or T? * | Bisexual women responses in Germany: Always open: 12%, selectively open: 62%, hide LGBT identity: 26%</t>
         </is>
       </c>
     </row>
@@ -1692,7 +1714,7 @@
       </c>
       <c r="F32" s="3" t="inlineStr">
         <is>
-          <t>Question b1_c — In your opinion, how widespread are expressions of hatred and aversion towards lesbian, gay, bisexual and/or transgender in public in the country where you live? | Poland responses (Transgender): Very widespread: 42%, Fairly widespread: 44%, Fairly rare: 12%, Very rare: 1%, Don`t know: 1%</t>
+          <t>Question c1a_d — In your opinion, in the country where you live, how widespread is discrimination because a person is Transgender? | Poland responses (Bisexual men): Very widespread: 69%, Fairly widespread: 16%, Fairly rare: 5%, Very rare: 1%, Don`t know: 9%</t>
         </is>
       </c>
     </row>
@@ -1714,7 +1736,7 @@
       </c>
       <c r="F33" s="5" t="inlineStr">
         <is>
-          <t>Question b1_c — In your opinion, how widespread are expressions of hatred and aversion towards lesbian, gay, bisexual and/or transgender in public in the country where you live? | Poland responses (Transgender): Very widespread: 42%, Fairly widespread: 44%, Fairly rare: 12%, Very rare: 1%, Don`t know: 1%</t>
+          <t>Question c1a_d — In your opinion, in the country where you live, how widespread is discrimination because a person is Transgender? | Poland responses (Bisexual men): Very widespread: 69%, Fairly widespread: 16%, Fairly rare: 5%, Very rare: 1%, Don`t know: 9%</t>
         </is>
       </c>
     </row>
@@ -1730,13 +1752,17 @@
       <c r="C34" s="2" t="n">
         <v>3</v>
       </c>
-      <c r="D34" s="3" t="inlineStr"/>
+      <c r="D34" s="3" t="inlineStr">
+        <is>
+          <t>C:\Users\RAZER\Desktop\portfolio-projects\1. RAG\data\3_txt_KB\LGBT_EU\by_country\LGBT_Survey_DailyLife\c1a_d_answer_by_Poland.txt</t>
+        </is>
+      </c>
       <c r="E34" s="2" t="b">
         <v>1</v>
       </c>
       <c r="F34" s="3" t="inlineStr">
         <is>
-          <t>Question b1_c — In your opinion, how widespread are expressions of hatred and aversion towards lesbian, gay, bisexual and/or transgender in public in the country where you live? | Poland responses (Transgender): Very widespread: 42%, Fairly widespread: 44%, Fairly rare: 12%, Very rare: 1%, Don`t know: 1%</t>
+          <t>Question c1a_d — In your opinion, in the country where you live, how widespread is discrimination because a person is Transgender? | Poland responses (Bisexual men): Very widespread: 69%, Fairly widespread: 16%, Fairly rare: 5%, Very rare: 1%, Don`t know: 9%</t>
         </is>
       </c>
     </row>
@@ -1754,7 +1780,7 @@
       </c>
       <c r="D35" s="5" t="inlineStr">
         <is>
-          <t>C:\Users\RAZER\Desktop\portfolio-projects\1. RAG\data\3_txt_KB\LGBT_EU\by_country\LGBT_Survey_DailyLife\b1_c_answer_by_Poland.txt</t>
+          <t>C:\Users\RAZER\Desktop\portfolio-projects\1. RAG\data\3_txt_KB\LGBT_EU\by_country\LGBT_Survey_DailyLife\c1a_d_answer_by_Poland.txt</t>
         </is>
       </c>
       <c r="E35" s="4" t="b">
@@ -1762,7 +1788,7 @@
       </c>
       <c r="F35" s="5" t="inlineStr">
         <is>
-          <t>Question b1_c — In your opinion, how widespread are expressions of hatred and aversion towards lesbian, gay, bisexual and/or transgender in public in the country where you live? | Poland responses (Transgender): Very widespread: 42%, Fairly widespread: 44%, Fairly rare: 12%, Very rare: 1%, Don`t know: 1%</t>
+          <t>Question c1a_d — In your opinion, in the country where you live, how widespread is discrimination because a person is Transgender? | Poland responses (Bisexual men): Very widespread: 69%, Fairly widespread: 16%, Fairly rare: 5%, Very rare: 1%, Don`t know: 9%</t>
         </is>
       </c>
     </row>
@@ -1780,7 +1806,7 @@
       </c>
       <c r="D36" s="3" t="inlineStr">
         <is>
-          <t>C:\Users\RAZER\Desktop\portfolio-projects\1. RAG\data\3_txt_KB\LGBT_EU\by_country\LGBT_Survey_DailyLife\b1_c_answer_by_Poland.txt</t>
+          <t>C:\Users\RAZER\Desktop\portfolio-projects\1. RAG\data\3_txt_KB\LGBT_EU\by_country\LGBT_Survey_DailyLife\c1a_d_answer_by_Poland.txt</t>
         </is>
       </c>
       <c r="E36" s="2" t="b">
@@ -1788,7 +1814,7 @@
       </c>
       <c r="F36" s="3" t="inlineStr">
         <is>
-          <t>Question b1_c — In your opinion, how widespread are expressions of hatred and aversion towards lesbian, gay, bisexual and/or transgender in public in the country where you live? | Poland responses (Transgender): Very widespread: 42%, Fairly widespread: 44%, Fairly rare: 12%, Very rare: 1%, Don`t know: 1%</t>
+          <t>Question c1a_d — In your opinion, in the country where you live, how widespread is discrimination because a person is Transgender? | Poland responses (Bisexual men): Very widespread: 69%, Fairly widespread: 16%, Fairly rare: 5%, Very rare: 1%, Don`t know: 9%</t>
         </is>
       </c>
     </row>
@@ -1806,7 +1832,7 @@
       </c>
       <c r="D37" s="5" t="inlineStr">
         <is>
-          <t>C:\Users\RAZER\Desktop\portfolio-projects\1. RAG\data\3_txt_KB\LGBT_EU\by_country\LGBT_Survey_DailyLife\b1_c_answer_by_Poland.txt</t>
+          <t>C:\Users\RAZER\Desktop\portfolio-projects\1. RAG\data\3_txt_KB\LGBT_EU\by_country\LGBT_Survey_DailyLife\c1a_d_answer_by_Poland.txt</t>
         </is>
       </c>
       <c r="E37" s="4" t="b">
@@ -1814,7 +1840,7 @@
       </c>
       <c r="F37" s="5" t="inlineStr">
         <is>
-          <t>Question b1_c — In your opinion, how widespread are expressions of hatred and aversion towards lesbian, gay, bisexual and/or transgender in public in the country where you live? | Poland responses (Transgender): Very widespread: 42%, Fairly widespread: 44%, Fairly rare: 12%, Very rare: 1%, Don`t know: 1%</t>
+          <t>Question c1a_d — In your opinion, in the country where you live, how widespread is discrimination because a person is Transgender? | Poland responses (Bisexual men): Very widespread: 69%, Fairly widespread: 16%, Fairly rare: 5%, Very rare: 1%, Don`t know: 9%</t>
         </is>
       </c>
     </row>
@@ -1832,7 +1858,7 @@
       </c>
       <c r="D38" s="3" t="inlineStr">
         <is>
-          <t>C:\Users\RAZER\Desktop\portfolio-projects\1. RAG\data\3_txt_KB\LGBT_EU\by_country\LGBT_Survey_DailyLife\b1_c_answer_by_Poland.txt</t>
+          <t>C:\Users\RAZER\Desktop\portfolio-projects\1. RAG\data\3_txt_KB\LGBT_EU\by_country\LGBT_Survey_DailyLife\c1a_d_answer_by_Poland.txt</t>
         </is>
       </c>
       <c r="E38" s="2" t="b">
@@ -1840,7 +1866,7 @@
       </c>
       <c r="F38" s="3" t="inlineStr">
         <is>
-          <t>Question b1_c — In your opinion, how widespread are expressions of hatred and aversion towards lesbian, gay, bisexual and/or transgender in public in the country where you live? | Poland responses (Transgender): Very widespread: 42%, Fairly widespread: 44%, Fairly rare: 12%, Very rare: 1%, Don`t know: 1%</t>
+          <t>Question c1a_d — In your opinion, in the country where you live, how widespread is discrimination because a person is Transgender? | Poland responses (Bisexual men): Very widespread: 69%, Fairly widespread: 16%, Fairly rare: 5%, Very rare: 1%, Don`t know: 9%</t>
         </is>
       </c>
     </row>
@@ -1856,13 +1882,17 @@
       <c r="C39" s="4" t="n">
         <v>8</v>
       </c>
-      <c r="D39" s="5" t="inlineStr"/>
+      <c r="D39" s="5" t="inlineStr">
+        <is>
+          <t>C:\Users\RAZER\Desktop\portfolio-projects\1. RAG\data\3_txt_KB\LGBT_EU\by_country\LGBT_Survey_DailyLife\c1a_d_answer_by_Poland.txt</t>
+        </is>
+      </c>
       <c r="E39" s="4" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="F39" s="5" t="inlineStr">
         <is>
-          <t>Question b1_c — In your opinion, how widespread are expressions of hatred and aversion towards lesbian, gay, bisexual and/or transgender in public in the country where you live? | Transgender responses in Poland: Very widespread: 42%, Fairly widespread: 44%, Fairly rare: 12%, Very rare: 1%, Don`t know: 1%</t>
+          <t>Question c1a_d — In your opinion, in the country where you live, how widespread is discrimination because a person is Transgender? | Poland responses (Bisexual men): Very widespread: 69%, Fairly widespread: 16%, Fairly rare: 5%, Very rare: 1%, Don`t know: 9%</t>
         </is>
       </c>
     </row>
@@ -1878,13 +1908,17 @@
       <c r="C40" s="2" t="n">
         <v>9</v>
       </c>
-      <c r="D40" s="3" t="inlineStr"/>
+      <c r="D40" s="3" t="inlineStr">
+        <is>
+          <t>C:\Users\RAZER\Desktop\portfolio-projects\1. RAG\data\3_txt_KB\LGBT_EU\by_country\LGBT_Survey_DailyLife\c1a_d_answer_by_Poland.txt</t>
+        </is>
+      </c>
       <c r="E40" s="2" t="b">
         <v>1</v>
       </c>
       <c r="F40" s="3" t="inlineStr">
         <is>
-          <t>Question b1_c — In your opinion, how widespread are expressions of hatred and aversion towards lesbian, gay, bisexual and/or transgender in public in the country where you live? | Transgender responses in Poland: Very widespread: 42%, Fairly widespread: 44%, Fairly rare: 12%, Very rare: 1%, Don`t know: 1%</t>
+          <t>Question c1a_d — In your opinion, in the country where you live, how widespread is discrimination because a person is Transgender? | Poland responses (Bisexual men): Very widespread: 69%, Fairly widespread: 16%, Fairly rare: 5%, Very rare: 1%, Don`t know: 9%</t>
         </is>
       </c>
     </row>
@@ -1900,13 +1934,17 @@
       <c r="C41" s="4" t="n">
         <v>10</v>
       </c>
-      <c r="D41" s="5" t="inlineStr"/>
+      <c r="D41" s="5" t="inlineStr">
+        <is>
+          <t>C:\Users\RAZER\Desktop\portfolio-projects\1. RAG\data\3_txt_KB\LGBT_EU\by_country\LGBT_Survey_DailyLife\c1a_d_answer_by_Poland.txt</t>
+        </is>
+      </c>
       <c r="E41" s="4" t="b">
         <v>1</v>
       </c>
       <c r="F41" s="5" t="inlineStr">
         <is>
-          <t>Question b1_c — In your opinion, how widespread are expressions of hatred and aversion towards lesbian, gay, bisexual and/or transgender in public in the country where you live? | Transgender responses in Poland: Very widespread: 42%, Fairly widespread: 44%, Fairly rare: 12%, Very rare: 1%, Don`t know: 1%</t>
+          <t>Question c1a_d — In your opinion, in the country where you live, how widespread is discrimination because a person is Transgender? | Poland responses (Bisexual men): Very widespread: 69%, Fairly widespread: 16%, Fairly rare: 5%, Very rare: 1%, Don`t know: 9%</t>
         </is>
       </c>
     </row>
@@ -1922,17 +1960,13 @@
       <c r="C42" s="2" t="n">
         <v>11</v>
       </c>
-      <c r="D42" s="3" t="inlineStr">
-        <is>
-          <t>C:\Users\RAZER\Desktop\portfolio-projects\1. RAG\data\3_txt_KB\LGBT_EU\by_subset\LGBT_Survey_DailyLife\b1_c_answer_by_Transgender.txt</t>
-        </is>
-      </c>
+      <c r="D42" s="3" t="inlineStr"/>
       <c r="E42" s="2" t="b">
         <v>1</v>
       </c>
       <c r="F42" s="3" t="inlineStr">
         <is>
-          <t>Question b1_c — In your opinion, how widespread are expressions of hatred and aversion towards lesbian, gay, bisexual and/or transgender in public in the country where you live? | Transgender responses in Poland: Very widespread: 42%, Fairly widespread: 44%, Fairly rare: 12%, Very rare: 1%, Don`t know: 1%</t>
+          <t>Question c1a_d — In your opinion, in the country where you live, how widespread is discrimination because a person is Transgender? | Poland responses (Bisexual men): Very widespread: 69%, Fairly widespread: 16%, Fairly rare: 5%, Very rare: 1%, Don`t know: 9%</t>
         </is>
       </c>
     </row>
@@ -1948,17 +1982,13 @@
       <c r="C43" s="4" t="n">
         <v>12</v>
       </c>
-      <c r="D43" s="5" t="inlineStr">
-        <is>
-          <t>C:\Users\RAZER\Desktop\portfolio-projects\1. RAG\data\3_txt_KB\LGBT_EU\by_subset\LGBT_Survey_DailyLife\b1_c_answer_by_Transgender.txt</t>
-        </is>
-      </c>
+      <c r="D43" s="5" t="inlineStr"/>
       <c r="E43" s="4" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="F43" s="5" t="inlineStr">
         <is>
-          <t>Question b1_c — In your opinion, how widespread are expressions of hatred and aversion towards lesbian, gay, bisexual and/or transgender in public in the country where you live? | Transgender responses in Poland: Very widespread: 42%, Fairly widespread: 44%, Fairly rare: 12%, Very rare: 1%, Don`t know: 1%</t>
+          <t>Question c1a_d — In your opinion, in the country where you live, how widespread is discrimination because a person is Transgender? | Poland responses (Bisexual women): Very widespread: 83%, Fairly widespread: 9%, Fairly rare: 3%, Very rare: 0%, Don`t know: 5%</t>
         </is>
       </c>
     </row>
@@ -1976,7 +2006,7 @@
       </c>
       <c r="D44" s="3" t="inlineStr">
         <is>
-          <t>C:\Users\RAZER\Desktop\portfolio-projects\1. RAG\data\3_txt_KB\LGBT_EU\by_subset\LGBT_Survey_DailyLife\b1_c_answer_by_Transgender.txt</t>
+          <t>C:\Users\RAZER\Desktop\portfolio-projects\1. RAG\data\3_txt_KB\LGBT_EU\by_country\LGBT_Survey_DailyLife\c1a_d_answer_by_Poland.txt</t>
         </is>
       </c>
       <c r="E44" s="2" t="b">
@@ -1984,7 +2014,7 @@
       </c>
       <c r="F44" s="3" t="inlineStr">
         <is>
-          <t>Question b1_c — In your opinion, how widespread are expressions of hatred and aversion towards lesbian, gay, bisexual and/or transgender in public in the country where you live? | Transgender responses in Poland: Very widespread: 42%, Fairly widespread: 44%, Fairly rare: 12%, Very rare: 1%, Don`t know: 1%</t>
+          <t>Question c1a_d — In your opinion, in the country where you live, how widespread is discrimination because a person is Transgender? | Poland responses (Bisexual women): Very widespread: 83%, Fairly widespread: 9%, Fairly rare: 3%, Very rare: 0%, Don`t know: 5%</t>
         </is>
       </c>
     </row>
@@ -2000,17 +2030,13 @@
       <c r="C45" s="4" t="n">
         <v>14</v>
       </c>
-      <c r="D45" s="5" t="inlineStr">
-        <is>
-          <t>C:\Users\RAZER\Desktop\portfolio-projects\1. RAG\data\3_txt_KB\LGBT_EU\by_subset\LGBT_Survey_DailyLife\b1_c_answer_by_Transgender.txt</t>
-        </is>
-      </c>
+      <c r="D45" s="5" t="inlineStr"/>
       <c r="E45" s="4" t="b">
         <v>1</v>
       </c>
       <c r="F45" s="5" t="inlineStr">
         <is>
-          <t>Question b1_c — In your opinion, how widespread are expressions of hatred and aversion towards lesbian, gay, bisexual and/or transgender in public in the country where you live? | Transgender responses in Poland: Very widespread: 42%, Fairly widespread: 44%, Fairly rare: 12%, Very rare: 1%, Don`t know: 1%</t>
+          <t>Question c1a_d — In your opinion, in the country where you live, how widespread is discrimination because a person is Transgender? | Poland responses (Bisexual women): Very widespread: 83%, Fairly widespread: 9%, Fairly rare: 3%, Very rare: 0%, Don`t know: 5%</t>
         </is>
       </c>
     </row>
@@ -2028,15 +2054,15 @@
       </c>
       <c r="D46" s="3" t="inlineStr">
         <is>
-          <t>C:\Users\RAZER\Desktop\portfolio-projects\1. RAG\data\3_txt_KB\LGBT_EU\by_country\LGBT_Survey_DailyLife\b1_d_answer_by_Poland.txt</t>
+          <t>C:\Users\RAZER\Desktop\portfolio-projects\1. RAG\data\3_txt_KB\LGBT_EU\by_country\LGBT_Survey_DailyLife\c1a_d_answer_by_Poland.txt</t>
         </is>
       </c>
       <c r="E46" s="2" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="F46" s="3" t="inlineStr">
         <is>
-          <t>Question b1_d — In your opinion, how widespread are assaults and harassment against lesbian, gay, bisexual and/or transgender people in the country where you live? | Poland responses (Transgender): Very widespread: 14%, Fairly widespread: 34%, Fairly rare: 29%, Very rare: 5%, Don`t know: 17%</t>
+          <t>Question c1a_d — In your opinion, in the country where you live, how widespread is discrimination because a person is Transgender? | Poland responses (Bisexual women): Very widespread: 83%, Fairly widespread: 9%, Fairly rare: 3%, Very rare: 0%, Don`t know: 5%</t>
         </is>
       </c>
     </row>
@@ -2224,15 +2250,15 @@
       </c>
       <c r="D54" s="3" t="inlineStr">
         <is>
-          <t>C:\Users\RAZER\Desktop\portfolio-projects\1. RAG\data\3_txt_KB\LGBT_EU\by_country\LGBT_Survey_DailyLife\b2_i_answer_by_Sweden.txt</t>
+          <t>C:\Users\RAZER\Desktop\portfolio-projects\1. RAG\data\3_txt_KB\LGBT_EU\by_subset\LGBT_Survey_DailyLife\b2_i_answer_by_Gay.txt</t>
         </is>
       </c>
       <c r="E54" s="2" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="F54" s="3" t="inlineStr">
         <is>
-          <t>Question b2_i — Recognition of same-sex partnerships across the European Union - What would allow you to be more comfortable living as a lesbian, gay or bisexual person in the country where you live? | Sweden responses (Gay): Strongly agree: 83%, Agree: 9%, Disagree: 2%, Strongly disagree: 1%, Current situation is fine: 3%, Don`t know: 3%</t>
+          <t>Question b2_i — Recognition of same-sex partnerships across the European Union - What would allow you to be more comfortable living as a lesbian, gay or bisexual person in the country where you live? | Gay responses in Sweden: Strongly agree: 83%, Agree: 9%, Disagree: 2%, Strongly disagree: 1%, Current situation is fine: 3%, Don`t know: 3%</t>
         </is>
       </c>
     </row>
@@ -2248,13 +2274,17 @@
       <c r="C55" s="4" t="n">
         <v>9</v>
       </c>
-      <c r="D55" s="5" t="inlineStr"/>
+      <c r="D55" s="5" t="inlineStr">
+        <is>
+          <t>C:\Users\RAZER\Desktop\portfolio-projects\1. RAG\data\3_txt_KB\LGBT_EU\by_subset\LGBT_Survey_DailyLife\b2_i_answer_by_Gay.txt</t>
+        </is>
+      </c>
       <c r="E55" s="4" t="b">
         <v>1</v>
       </c>
       <c r="F55" s="5" t="inlineStr">
         <is>
-          <t>Question b2_i — Recognition of same-sex partnerships across the European Union - What would allow you to be more comfortable living as a lesbian, gay or bisexual person in the country where you live? | Sweden responses (Gay): Strongly agree: 83%, Agree: 9%, Disagree: 2%, Strongly disagree: 1%, Current situation is fine: 3%, Don`t know: 3%</t>
+          <t>Question b2_i — Recognition of same-sex partnerships across the European Union - What would allow you to be more comfortable living as a lesbian, gay or bisexual person in the country where you live? | Gay responses in Sweden: Strongly agree: 83%, Agree: 9%, Disagree: 2%, Strongly disagree: 1%, Current situation is fine: 3%, Don`t know: 3%</t>
         </is>
       </c>
     </row>
@@ -2270,13 +2300,17 @@
       <c r="C56" s="2" t="n">
         <v>10</v>
       </c>
-      <c r="D56" s="3" t="inlineStr"/>
+      <c r="D56" s="3" t="inlineStr">
+        <is>
+          <t>C:\Users\RAZER\Desktop\portfolio-projects\1. RAG\data\3_txt_KB\LGBT_EU\by_subset\LGBT_Survey_DailyLife\b2_i_answer_by_Gay.txt</t>
+        </is>
+      </c>
       <c r="E56" s="2" t="b">
         <v>1</v>
       </c>
       <c r="F56" s="3" t="inlineStr">
         <is>
-          <t>Question b2_i — Recognition of same-sex partnerships across the European Union - What would allow you to be more comfortable living as a lesbian, gay or bisexual person in the country where you live? | Sweden responses (Gay): Strongly agree: 83%, Agree: 9%, Disagree: 2%, Strongly disagree: 1%, Current situation is fine: 3%, Don`t know: 3%</t>
+          <t>Question b2_i — Recognition of same-sex partnerships across the European Union - What would allow you to be more comfortable living as a lesbian, gay or bisexual person in the country where you live? | Gay responses in Sweden: Strongly agree: 83%, Agree: 9%, Disagree: 2%, Strongly disagree: 1%, Current situation is fine: 3%, Don`t know: 3%</t>
         </is>
       </c>
     </row>
@@ -2292,13 +2326,17 @@
       <c r="C57" s="4" t="n">
         <v>11</v>
       </c>
-      <c r="D57" s="5" t="inlineStr"/>
+      <c r="D57" s="5" t="inlineStr">
+        <is>
+          <t>C:\Users\RAZER\Desktop\portfolio-projects\1. RAG\data\3_txt_KB\LGBT_EU\by_subset\LGBT_Survey_DailyLife\b2_i_answer_by_Gay.txt</t>
+        </is>
+      </c>
       <c r="E57" s="4" t="b">
         <v>1</v>
       </c>
       <c r="F57" s="5" t="inlineStr">
         <is>
-          <t>Question b2_i — Recognition of same-sex partnerships across the European Union - What would allow you to be more comfortable living as a lesbian, gay or bisexual person in the country where you live? | Sweden responses (Gay): Strongly agree: 83%, Agree: 9%, Disagree: 2%, Strongly disagree: 1%, Current situation is fine: 3%, Don`t know: 3%</t>
+          <t>Question b2_i — Recognition of same-sex partnerships across the European Union - What would allow you to be more comfortable living as a lesbian, gay or bisexual person in the country where you live? | Gay responses in Sweden: Strongly agree: 83%, Agree: 9%, Disagree: 2%, Strongly disagree: 1%, Current situation is fine: 3%, Don`t know: 3%</t>
         </is>
       </c>
     </row>
@@ -2320,7 +2358,7 @@
         </is>
       </c>
       <c r="E58" s="2" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="F58" s="3" t="inlineStr">
         <is>
@@ -2340,11 +2378,7 @@
       <c r="C59" s="4" t="n">
         <v>13</v>
       </c>
-      <c r="D59" s="5" t="inlineStr">
-        <is>
-          <t>C:\Users\RAZER\Desktop\portfolio-projects\1. RAG\data\3_txt_KB\LGBT_EU\by_country\LGBT_Survey_DailyLife\b2_i_answer_by_Sweden.txt</t>
-        </is>
-      </c>
+      <c r="D59" s="5" t="inlineStr"/>
       <c r="E59" s="4" t="b">
         <v>1</v>
       </c>
@@ -2366,11 +2400,7 @@
       <c r="C60" s="2" t="n">
         <v>14</v>
       </c>
-      <c r="D60" s="3" t="inlineStr">
-        <is>
-          <t>C:\Users\RAZER\Desktop\portfolio-projects\1. RAG\data\3_txt_KB\LGBT_EU\by_country\LGBT_Survey_DailyLife\b2_i_answer_by_Sweden.txt</t>
-        </is>
-      </c>
+      <c r="D60" s="3" t="inlineStr"/>
       <c r="E60" s="2" t="b">
         <v>1</v>
       </c>
@@ -2392,13 +2422,17 @@
       <c r="C61" s="4" t="n">
         <v>15</v>
       </c>
-      <c r="D61" s="5" t="inlineStr"/>
+      <c r="D61" s="5" t="inlineStr">
+        <is>
+          <t>C:\Users\RAZER\Desktop\portfolio-projects\1. RAG\data\3_txt_KB\LGBT_EU\by_country\LGBT_Survey_DailyLife\b2_i_answer_by_Sweden.txt</t>
+        </is>
+      </c>
       <c r="E61" s="4" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="F61" s="5" t="inlineStr">
         <is>
-          <t>Question b2_i — Recognition of same-sex partnerships across the European Union - What would allow you to be more comfortable living as a lesbian, gay or bisexual person in the country where you live? | Sweden responses (Bisexual men): Strongly agree: 66%, Agree: 20%, Disagree: 3%, Strongly disagree: 1%, Current situation is fine: 2%, Don`t know: 8%</t>
+          <t>Question b2_i — Recognition of same-sex partnerships across the European Union - What would allow you to be more comfortable living as a lesbian, gay or bisexual person in the country where you live? | Sweden responses (Gay): Strongly agree: 83%, Agree: 9%, Disagree: 2%, Strongly disagree: 1%, Current situation is fine: 3%, Don`t know: 3%</t>
         </is>
       </c>
     </row>
@@ -2414,24 +2448,22 @@
       <c r="C62" s="2" t="n">
         <v>1</v>
       </c>
-      <c r="D62" s="3" t="inlineStr"/>
+      <c r="D62" s="3" t="inlineStr">
+        <is>
+          <t>C:\Users\RAZER\Desktop\portfolio-projects\1. RAG\data\3_txt_KB\HIV_AIDS_data\art_coverage_by_country_clean_Luxembourg.txt</t>
+        </is>
+      </c>
       <c r="E62" s="2" t="b">
         <v>0</v>
       </c>
       <c r="F62" s="3" t="inlineStr">
         <is>
-          <t>HEPB3 coverage in Belgium (2011): 97.0%
-HEPB3 coverage in Belgium (2012): 98.0%
-HEPB3 coverage in Belgium (2013): 98.0%
-HEPB3 coverage in Belgium (2014): 98.0%
-HEPB3 coverage in Belgium (2015): 98.0%
-HEPB3 coverage in Belgium (2016): 97.0%
-HEPB3 coverage in Belgium (2017): 97.0%
-HEPB3 coverage in Belgium (2018): 97.0%
-HEPB3 coverage in Belgium (2019): 97.0%
-HEPB3 coverage in Belgium (2020): 97.0%
-HEPB3 coverage in Belgium (2021): 97.0%
-HEPB3 coverage in Belgium (2022): 97.0%</t>
+          <t>Reported number of people receiving ART in Luxembourg: 890
+Estimated number of people living with HIV_median in Luxembourg: 1200.0
+Estimated number of people living with HIV_min in Luxembourg: 1000.0
+Estimated number of people living with HIV_max in Luxembourg: 1300.0
+Estimated ART coverage among people living with HIV (%)_median in Luxembourg: 77.0
+Estimated ART coverage among people living with HIV (%)_min in Luxembourg: 67.0</t>
         </is>
       </c>
     </row>
@@ -2447,24 +2479,22 @@
       <c r="C63" s="4" t="n">
         <v>2</v>
       </c>
-      <c r="D63" s="5" t="inlineStr"/>
+      <c r="D63" s="5" t="inlineStr">
+        <is>
+          <t>C:\Users\RAZER\Desktop\portfolio-projects\1. RAG\data\3_txt_KB\HIV_AIDS_data\art_coverage_by_country_clean_Luxembourg.txt</t>
+        </is>
+      </c>
       <c r="E63" s="4" t="b">
         <v>1</v>
       </c>
       <c r="F63" s="5" t="inlineStr">
         <is>
-          <t>HEPB3 coverage in Belgium (2011): 97.0%
-HEPB3 coverage in Belgium (2012): 98.0%
-HEPB3 coverage in Belgium (2013): 98.0%
-HEPB3 coverage in Belgium (2014): 98.0%
-HEPB3 coverage in Belgium (2015): 98.0%
-HEPB3 coverage in Belgium (2016): 97.0%
-HEPB3 coverage in Belgium (2017): 97.0%
-HEPB3 coverage in Belgium (2018): 97.0%
-HEPB3 coverage in Belgium (2019): 97.0%
-HEPB3 coverage in Belgium (2020): 97.0%
-HEPB3 coverage in Belgium (2021): 97.0%
-HEPB3 coverage in Belgium (2022): 97.0%</t>
+          <t>Reported number of people receiving ART in Luxembourg: 890
+Estimated number of people living with HIV_median in Luxembourg: 1200.0
+Estimated number of people living with HIV_min in Luxembourg: 1000.0
+Estimated number of people living with HIV_max in Luxembourg: 1300.0
+Estimated ART coverage among people living with HIV (%)_median in Luxembourg: 77.0
+Estimated ART coverage among people living with HIV (%)_min in Luxembourg: 67.0</t>
         </is>
       </c>
     </row>
@@ -2480,28 +2510,18 @@
       <c r="C64" s="2" t="n">
         <v>3</v>
       </c>
-      <c r="D64" s="3" t="inlineStr">
-        <is>
-          <t>C:\Users\RAZER\Desktop\portfolio-projects\1. RAG\data\3_txt_KB\UNICEF_Immunization\HEPB3_Belgium.txt</t>
-        </is>
-      </c>
+      <c r="D64" s="3" t="inlineStr"/>
       <c r="E64" s="2" t="b">
         <v>1</v>
       </c>
       <c r="F64" s="3" t="inlineStr">
         <is>
-          <t>HEPB3 coverage in Belgium (2011): 97.0%
-HEPB3 coverage in Belgium (2012): 98.0%
-HEPB3 coverage in Belgium (2013): 98.0%
-HEPB3 coverage in Belgium (2014): 98.0%
-HEPB3 coverage in Belgium (2015): 98.0%
-HEPB3 coverage in Belgium (2016): 97.0%
-HEPB3 coverage in Belgium (2017): 97.0%
-HEPB3 coverage in Belgium (2018): 97.0%
-HEPB3 coverage in Belgium (2019): 97.0%
-HEPB3 coverage in Belgium (2020): 97.0%
-HEPB3 coverage in Belgium (2021): 97.0%
-HEPB3 coverage in Belgium (2022): 97.0%</t>
+          <t>Reported number of people receiving ART in Luxembourg: 890
+Estimated number of people living with HIV_median in Luxembourg: 1200.0
+Estimated number of people living with HIV_min in Luxembourg: 1000.0
+Estimated number of people living with HIV_max in Luxembourg: 1300.0
+Estimated ART coverage among people living with HIV (%)_median in Luxembourg: 77.0
+Estimated ART coverage among people living with HIV (%)_min in Luxembourg: 67.0</t>
         </is>
       </c>
     </row>
@@ -2517,28 +2537,18 @@
       <c r="C65" s="4" t="n">
         <v>4</v>
       </c>
-      <c r="D65" s="5" t="inlineStr">
-        <is>
-          <t>C:\Users\RAZER\Desktop\portfolio-projects\1. RAG\data\3_txt_KB\UNICEF_Immunization\HEPB3_Belgium.txt</t>
-        </is>
-      </c>
+      <c r="D65" s="5" t="inlineStr"/>
       <c r="E65" s="4" t="b">
         <v>1</v>
       </c>
       <c r="F65" s="5" t="inlineStr">
         <is>
-          <t>HEPB3 coverage in Belgium (2011): 97.0%
-HEPB3 coverage in Belgium (2012): 98.0%
-HEPB3 coverage in Belgium (2013): 98.0%
-HEPB3 coverage in Belgium (2014): 98.0%
-HEPB3 coverage in Belgium (2015): 98.0%
-HEPB3 coverage in Belgium (2016): 97.0%
-HEPB3 coverage in Belgium (2017): 97.0%
-HEPB3 coverage in Belgium (2018): 97.0%
-HEPB3 coverage in Belgium (2019): 97.0%
-HEPB3 coverage in Belgium (2020): 97.0%
-HEPB3 coverage in Belgium (2021): 97.0%
-HEPB3 coverage in Belgium (2022): 97.0%</t>
+          <t>Reported number of people receiving ART in Luxembourg: 890
+Estimated number of people living with HIV_median in Luxembourg: 1200.0
+Estimated number of people living with HIV_min in Luxembourg: 1000.0
+Estimated number of people living with HIV_max in Luxembourg: 1300.0
+Estimated ART coverage among people living with HIV (%)_median in Luxembourg: 77.0
+Estimated ART coverage among people living with HIV (%)_min in Luxembourg: 67.0</t>
         </is>
       </c>
     </row>
@@ -2554,28 +2564,18 @@
       <c r="C66" s="2" t="n">
         <v>5</v>
       </c>
-      <c r="D66" s="3" t="inlineStr">
-        <is>
-          <t>C:\Users\RAZER\Desktop\portfolio-projects\1. RAG\data\3_txt_KB\UNICEF_Immunization\HEPB3_Belgium.txt</t>
-        </is>
-      </c>
+      <c r="D66" s="3" t="inlineStr"/>
       <c r="E66" s="2" t="b">
         <v>1</v>
       </c>
       <c r="F66" s="3" t="inlineStr">
         <is>
-          <t>HEPB3 coverage in Belgium (2011): 97.0%
-HEPB3 coverage in Belgium (2012): 98.0%
-HEPB3 coverage in Belgium (2013): 98.0%
-HEPB3 coverage in Belgium (2014): 98.0%
-HEPB3 coverage in Belgium (2015): 98.0%
-HEPB3 coverage in Belgium (2016): 97.0%
-HEPB3 coverage in Belgium (2017): 97.0%
-HEPB3 coverage in Belgium (2018): 97.0%
-HEPB3 coverage in Belgium (2019): 97.0%
-HEPB3 coverage in Belgium (2020): 97.0%
-HEPB3 coverage in Belgium (2021): 97.0%
-HEPB3 coverage in Belgium (2022): 97.0%</t>
+          <t>Reported number of people receiving ART in Luxembourg: 890
+Estimated number of people living with HIV_median in Luxembourg: 1200.0
+Estimated number of people living with HIV_min in Luxembourg: 1000.0
+Estimated number of people living with HIV_max in Luxembourg: 1300.0
+Estimated ART coverage among people living with HIV (%)_median in Luxembourg: 77.0
+Estimated ART coverage among people living with HIV (%)_min in Luxembourg: 67.0</t>
         </is>
       </c>
     </row>
@@ -2591,24 +2591,22 @@
       <c r="C67" s="4" t="n">
         <v>6</v>
       </c>
-      <c r="D67" s="5" t="inlineStr"/>
+      <c r="D67" s="5" t="inlineStr">
+        <is>
+          <t>C:\Users\RAZER\Desktop\portfolio-projects\1. RAG\data\3_txt_KB\HIV_AIDS_data\art_coverage_by_country_clean_Luxembourg.txt</t>
+        </is>
+      </c>
       <c r="E67" s="4" t="b">
         <v>1</v>
       </c>
       <c r="F67" s="5" t="inlineStr">
         <is>
-          <t>HEPB3 coverage in Belgium (2011): 97.0%
-HEPB3 coverage in Belgium (2012): 98.0%
-HEPB3 coverage in Belgium (2013): 98.0%
-HEPB3 coverage in Belgium (2014): 98.0%
-HEPB3 coverage in Belgium (2015): 98.0%
-HEPB3 coverage in Belgium (2016): 97.0%
-HEPB3 coverage in Belgium (2017): 97.0%
-HEPB3 coverage in Belgium (2018): 97.0%
-HEPB3 coverage in Belgium (2019): 97.0%
-HEPB3 coverage in Belgium (2020): 97.0%
-HEPB3 coverage in Belgium (2021): 97.0%
-HEPB3 coverage in Belgium (2022): 97.0%</t>
+          <t>Reported number of people receiving ART in Luxembourg: 890
+Estimated number of people living with HIV_median in Luxembourg: 1200.0
+Estimated number of people living with HIV_min in Luxembourg: 1000.0
+Estimated number of people living with HIV_max in Luxembourg: 1300.0
+Estimated ART coverage among people living with HIV (%)_median in Luxembourg: 77.0
+Estimated ART coverage among people living with HIV (%)_min in Luxembourg: 67.0</t>
         </is>
       </c>
     </row>
@@ -2624,24 +2622,22 @@
       <c r="C68" s="2" t="n">
         <v>7</v>
       </c>
-      <c r="D68" s="3" t="inlineStr"/>
+      <c r="D68" s="3" t="inlineStr">
+        <is>
+          <t>C:\Users\RAZER\Desktop\portfolio-projects\1. RAG\data\3_txt_KB\HIV_AIDS_data\art_coverage_by_country_clean_Luxembourg.txt</t>
+        </is>
+      </c>
       <c r="E68" s="2" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="F68" s="3" t="inlineStr">
         <is>
-          <t>HEPB3 coverage in Belgium (2000): 60.0%
-HEPB3 coverage in Belgium (2001): 60.0%
-HEPB3 coverage in Belgium (2002): 60.0%
-HEPB3 coverage in Belgium (2003): 64.0%
-HEPB3 coverage in Belgium (2004): 64.0%
-HEPB3 coverage in Belgium (2005): 77.0%
-HEPB3 coverage in Belgium (2006): 94.0%
-HEPB3 coverage in Belgium (2007): 94.0%
-HEPB3 coverage in Belgium (2008): 98.0%
-HEPB3 coverage in Belgium (2009): 97.0%
-HEPB3 coverage in Belgium (2010): 97.0%
-HEPB3 coverage in Belgium (2011): 97.0%</t>
+          <t>Reported number of people receiving ART in Luxembourg: 890
+Estimated number of people living with HIV_median in Luxembourg: 1200.0
+Estimated number of people living with HIV_min in Luxembourg: 1000.0
+Estimated number of people living with HIV_max in Luxembourg: 1300.0
+Estimated ART coverage among people living with HIV (%)_median in Luxembourg: 77.0
+Estimated ART coverage among people living with HIV (%)_min in Luxembourg: 67.0</t>
         </is>
       </c>
     </row>
@@ -2657,24 +2653,22 @@
       <c r="C69" s="4" t="n">
         <v>8</v>
       </c>
-      <c r="D69" s="5" t="inlineStr"/>
+      <c r="D69" s="5" t="inlineStr">
+        <is>
+          <t>C:\Users\RAZER\Desktop\portfolio-projects\1. RAG\data\3_txt_KB\HIV_AIDS_data\art_coverage_by_country_clean_Luxembourg.txt</t>
+        </is>
+      </c>
       <c r="E69" s="4" t="b">
         <v>1</v>
       </c>
       <c r="F69" s="5" t="inlineStr">
         <is>
-          <t>HEPB3 coverage in Belgium (2000): 60.0%
-HEPB3 coverage in Belgium (2001): 60.0%
-HEPB3 coverage in Belgium (2002): 60.0%
-HEPB3 coverage in Belgium (2003): 64.0%
-HEPB3 coverage in Belgium (2004): 64.0%
-HEPB3 coverage in Belgium (2005): 77.0%
-HEPB3 coverage in Belgium (2006): 94.0%
-HEPB3 coverage in Belgium (2007): 94.0%
-HEPB3 coverage in Belgium (2008): 98.0%
-HEPB3 coverage in Belgium (2009): 97.0%
-HEPB3 coverage in Belgium (2010): 97.0%
-HEPB3 coverage in Belgium (2011): 97.0%</t>
+          <t>Reported number of people receiving ART in Luxembourg: 890
+Estimated number of people living with HIV_median in Luxembourg: 1200.0
+Estimated number of people living with HIV_min in Luxembourg: 1000.0
+Estimated number of people living with HIV_max in Luxembourg: 1300.0
+Estimated ART coverage among people living with HIV (%)_median in Luxembourg: 77.0
+Estimated ART coverage among people living with HIV (%)_min in Luxembourg: 67.0</t>
         </is>
       </c>
     </row>
@@ -2692,7 +2686,7 @@
       </c>
       <c r="D70" s="3" t="inlineStr">
         <is>
-          <t>C:\Users\RAZER\Desktop\portfolio-projects\1. RAG\data\3_txt_KB\UNICEF_Immunization\HEPB3_Belgium.txt</t>
+          <t>C:\Users\RAZER\Desktop\portfolio-projects\1. RAG\data\3_txt_KB\HIV_AIDS_data\art_coverage_by_country_clean_Luxembourg.txt</t>
         </is>
       </c>
       <c r="E70" s="2" t="b">
@@ -2700,18 +2694,12 @@
       </c>
       <c r="F70" s="3" t="inlineStr">
         <is>
-          <t>HEPB3 coverage in Belgium (2000): 60.0%
-HEPB3 coverage in Belgium (2001): 60.0%
-HEPB3 coverage in Belgium (2002): 60.0%
-HEPB3 coverage in Belgium (2003): 64.0%
-HEPB3 coverage in Belgium (2004): 64.0%
-HEPB3 coverage in Belgium (2005): 77.0%
-HEPB3 coverage in Belgium (2006): 94.0%
-HEPB3 coverage in Belgium (2007): 94.0%
-HEPB3 coverage in Belgium (2008): 98.0%
-HEPB3 coverage in Belgium (2009): 97.0%
-HEPB3 coverage in Belgium (2010): 97.0%
-HEPB3 coverage in Belgium (2011): 97.0%</t>
+          <t>Reported number of people receiving ART in Luxembourg: 890
+Estimated number of people living with HIV_median in Luxembourg: 1200.0
+Estimated number of people living with HIV_min in Luxembourg: 1000.0
+Estimated number of people living with HIV_max in Luxembourg: 1300.0
+Estimated ART coverage among people living with HIV (%)_median in Luxembourg: 77.0
+Estimated ART coverage among people living with HIV (%)_min in Luxembourg: 67.0</t>
         </is>
       </c>
     </row>
@@ -2729,26 +2717,15 @@
       </c>
       <c r="D71" s="5" t="inlineStr">
         <is>
-          <t>C:\Users\RAZER\Desktop\portfolio-projects\1. RAG\data\3_txt_KB\UNICEF_Immunization\HEPB3_Belgium.txt</t>
+          <t>C:\Users\RAZER\Desktop\portfolio-projects\1. RAG\data\3_txt_KB\HIV_AIDS_data\art_coverage_by_country_clean_Luxembourg.txt</t>
         </is>
       </c>
       <c r="E71" s="4" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="F71" s="5" t="inlineStr">
         <is>
-          <t>HEPB3 coverage in Belgium (2000): 60.0%
-HEPB3 coverage in Belgium (2001): 60.0%
-HEPB3 coverage in Belgium (2002): 60.0%
-HEPB3 coverage in Belgium (2003): 64.0%
-HEPB3 coverage in Belgium (2004): 64.0%
-HEPB3 coverage in Belgium (2005): 77.0%
-HEPB3 coverage in Belgium (2006): 94.0%
-HEPB3 coverage in Belgium (2007): 94.0%
-HEPB3 coverage in Belgium (2008): 98.0%
-HEPB3 coverage in Belgium (2009): 97.0%
-HEPB3 coverage in Belgium (2010): 97.0%
-HEPB3 coverage in Belgium (2011): 97.0%</t>
+          <t>Estimated ART coverage among people living with HIV (%)_max in Luxembourg: 86.0</t>
         </is>
       </c>
     </row>
@@ -2764,28 +2741,13 @@
       <c r="C72" s="2" t="n">
         <v>11</v>
       </c>
-      <c r="D72" s="3" t="inlineStr">
-        <is>
-          <t>C:\Users\RAZER\Desktop\portfolio-projects\1. RAG\data\3_txt_KB\UNICEF_Immunization\HEPB3_Belgium.txt</t>
-        </is>
-      </c>
+      <c r="D72" s="3" t="inlineStr"/>
       <c r="E72" s="2" t="b">
         <v>1</v>
       </c>
       <c r="F72" s="3" t="inlineStr">
         <is>
-          <t>HEPB3 coverage in Belgium (2000): 60.0%
-HEPB3 coverage in Belgium (2001): 60.0%
-HEPB3 coverage in Belgium (2002): 60.0%
-HEPB3 coverage in Belgium (2003): 64.0%
-HEPB3 coverage in Belgium (2004): 64.0%
-HEPB3 coverage in Belgium (2005): 77.0%
-HEPB3 coverage in Belgium (2006): 94.0%
-HEPB3 coverage in Belgium (2007): 94.0%
-HEPB3 coverage in Belgium (2008): 98.0%
-HEPB3 coverage in Belgium (2009): 97.0%
-HEPB3 coverage in Belgium (2010): 97.0%
-HEPB3 coverage in Belgium (2011): 97.0%</t>
+          <t>Estimated ART coverage among people living with HIV (%)_max in Luxembourg: 86.0</t>
         </is>
       </c>
     </row>
@@ -2807,18 +2769,7 @@
       </c>
       <c r="F73" s="5" t="inlineStr">
         <is>
-          <t>HEPB3 coverage in Belgium (2000): 60.0%
-HEPB3 coverage in Belgium (2001): 60.0%
-HEPB3 coverage in Belgium (2002): 60.0%
-HEPB3 coverage in Belgium (2003): 64.0%
-HEPB3 coverage in Belgium (2004): 64.0%
-HEPB3 coverage in Belgium (2005): 77.0%
-HEPB3 coverage in Belgium (2006): 94.0%
-HEPB3 coverage in Belgium (2007): 94.0%
-HEPB3 coverage in Belgium (2008): 98.0%
-HEPB3 coverage in Belgium (2009): 97.0%
-HEPB3 coverage in Belgium (2010): 97.0%
-HEPB3 coverage in Belgium (2011): 97.0%</t>
+          <t>Estimated ART coverage among people living with HIV (%)_max in Luxembourg: 86.0</t>
         </is>
       </c>
     </row>
@@ -2836,12 +2787,11 @@
       </c>
       <c r="D74" s="3" t="inlineStr"/>
       <c r="E74" s="2" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="F74" s="3" t="inlineStr">
         <is>
-          <t>HEPB3 coverage in Belgium (2022): 97.0%
-HEPB3 coverage in Belgium (2023): 97.0%</t>
+          <t>Estimated ART coverage among people living with HIV (%)_max in Luxembourg: 86.0</t>
         </is>
       </c>
     </row>
@@ -2859,7 +2809,7 @@
       </c>
       <c r="D75" s="5" t="inlineStr">
         <is>
-          <t>C:\Users\RAZER\Desktop\portfolio-projects\1. RAG\data\3_txt_KB\UNICEF_Immunization\HEPB3_Belgium.txt</t>
+          <t>C:\Users\RAZER\Desktop\portfolio-projects\1. RAG\data\3_txt_KB\HIV_AIDS_data\art_coverage_by_country_clean_Luxembourg.txt</t>
         </is>
       </c>
       <c r="E75" s="4" t="b">
@@ -2867,8 +2817,7 @@
       </c>
       <c r="F75" s="5" t="inlineStr">
         <is>
-          <t>HEPB3 coverage in Belgium (2022): 97.0%
-HEPB3 coverage in Belgium (2023): 97.0%</t>
+          <t>Estimated ART coverage among people living with HIV (%)_max in Luxembourg: 86.0</t>
         </is>
       </c>
     </row>
@@ -2886,7 +2835,7 @@
       </c>
       <c r="D76" s="3" t="inlineStr">
         <is>
-          <t>C:\Users\RAZER\Desktop\portfolio-projects\1. RAG\data\3_txt_KB\UNICEF_Immunization\HEPB3_Belgium.txt</t>
+          <t>C:\Users\RAZER\Desktop\portfolio-projects\1. RAG\data\3_txt_KB\HIV_AIDS_data\art_coverage_by_country_clean_Luxembourg.txt</t>
         </is>
       </c>
       <c r="E76" s="2" t="b">
@@ -2894,8 +2843,7 @@
       </c>
       <c r="F76" s="3" t="inlineStr">
         <is>
-          <t>HEPB3 coverage in Belgium (2022): 97.0%
-HEPB3 coverage in Belgium (2023): 97.0%</t>
+          <t>Estimated ART coverage among people living with HIV (%)_max in Luxembourg: 86.0</t>
         </is>
       </c>
     </row>
@@ -2911,7 +2859,11 @@
       <c r="C77" s="4" t="n">
         <v>1</v>
       </c>
-      <c r="D77" s="5" t="inlineStr"/>
+      <c r="D77" s="5" t="inlineStr">
+        <is>
+          <t>C:\Users\RAZER\Desktop\portfolio-projects\1. RAG\data\3_txt_KB\HIV_AIDS_data\art_coverage_by_country_clean_Croatia.txt</t>
+        </is>
+      </c>
       <c r="E77" s="4" t="b">
         <v>0</v>
       </c>
@@ -2967,11 +2919,7 @@
       <c r="C79" s="4" t="n">
         <v>3</v>
       </c>
-      <c r="D79" s="5" t="inlineStr">
-        <is>
-          <t>C:\Users\RAZER\Desktop\portfolio-projects\1. RAG\data\3_txt_KB\HIV_AIDS_data\art_coverage_by_country_clean_Croatia.txt</t>
-        </is>
-      </c>
+      <c r="D79" s="5" t="inlineStr"/>
       <c r="E79" s="4" t="b">
         <v>1</v>
       </c>
@@ -3063,7 +3011,11 @@
       <c r="C82" s="2" t="n">
         <v>6</v>
       </c>
-      <c r="D82" s="3" t="inlineStr"/>
+      <c r="D82" s="3" t="inlineStr">
+        <is>
+          <t>C:\Users\RAZER\Desktop\portfolio-projects\1. RAG\data\3_txt_KB\HIV_AIDS_data\art_coverage_by_country_clean_Croatia.txt</t>
+        </is>
+      </c>
       <c r="E82" s="2" t="b">
         <v>1</v>
       </c>
@@ -3123,11 +3075,167 @@
       <c r="C84" s="2" t="n">
         <v>8</v>
       </c>
-      <c r="D84" s="3" t="inlineStr"/>
+      <c r="D84" s="3" t="inlineStr">
+        <is>
+          <t>C:\Users\RAZER\Desktop\portfolio-projects\1. RAG\data\3_txt_KB\HIV_AIDS_data\art_coverage_by_country_clean_Croatia.txt</t>
+        </is>
+      </c>
       <c r="E84" s="2" t="b">
+        <v>1</v>
+      </c>
+      <c r="F84" s="3" t="inlineStr">
+        <is>
+          <t>Reported number of people receiving ART in Croatia: 1200
+Estimated number of people living with HIV_median in Croatia: 1600.0
+Estimated number of people living with HIV_min in Croatia: 1400.0
+Estimated number of people living with HIV_max in Croatia: 1700.0
+Estimated ART coverage among people living with HIV (%)_median in Croatia: 75.0
+Estimated ART coverage among people living with HIV (%)_min in Croatia: 67.0
+Estimated ART coverage among people living with HIV (%)_max in Croatia: 83.0</t>
+        </is>
+      </c>
+    </row>
+    <row r="85">
+      <c r="A85" s="4" t="n">
+        <v>6</v>
+      </c>
+      <c r="B85" s="5" t="inlineStr">
+        <is>
+          <t>What barriers to HIV &amp; AIDS treatment exist in Bosnia and Herzegovina?</t>
+        </is>
+      </c>
+      <c r="C85" s="4" t="n">
+        <v>9</v>
+      </c>
+      <c r="D85" s="5" t="inlineStr">
+        <is>
+          <t>C:\Users\RAZER\Desktop\portfolio-projects\1. RAG\data\3_txt_KB\HIV_AIDS_data\art_coverage_by_country_clean_Croatia.txt</t>
+        </is>
+      </c>
+      <c r="E85" s="4" t="b">
+        <v>1</v>
+      </c>
+      <c r="F85" s="5" t="inlineStr">
+        <is>
+          <t>Reported number of people receiving ART in Croatia: 1200
+Estimated number of people living with HIV_median in Croatia: 1600.0
+Estimated number of people living with HIV_min in Croatia: 1400.0
+Estimated number of people living with HIV_max in Croatia: 1700.0
+Estimated ART coverage among people living with HIV (%)_median in Croatia: 75.0
+Estimated ART coverage among people living with HIV (%)_min in Croatia: 67.0
+Estimated ART coverage among people living with HIV (%)_max in Croatia: 83.0</t>
+        </is>
+      </c>
+    </row>
+    <row r="86">
+      <c r="A86" s="2" t="n">
+        <v>6</v>
+      </c>
+      <c r="B86" s="3" t="inlineStr">
+        <is>
+          <t>What barriers to HIV &amp; AIDS treatment exist in Bosnia and Herzegovina?</t>
+        </is>
+      </c>
+      <c r="C86" s="2" t="n">
+        <v>10</v>
+      </c>
+      <c r="D86" s="3" t="inlineStr">
+        <is>
+          <t>C:\Users\RAZER\Desktop\portfolio-projects\1. RAG\data\3_txt_KB\HIV_AIDS_data\art_coverage_by_country_clean_Croatia.txt</t>
+        </is>
+      </c>
+      <c r="E86" s="2" t="b">
+        <v>1</v>
+      </c>
+      <c r="F86" s="3" t="inlineStr">
+        <is>
+          <t>Reported number of people receiving ART in Croatia: 1200
+Estimated number of people living with HIV_median in Croatia: 1600.0
+Estimated number of people living with HIV_min in Croatia: 1400.0
+Estimated number of people living with HIV_max in Croatia: 1700.0
+Estimated ART coverage among people living with HIV (%)_median in Croatia: 75.0
+Estimated ART coverage among people living with HIV (%)_min in Croatia: 67.0
+Estimated ART coverage among people living with HIV (%)_max in Croatia: 83.0</t>
+        </is>
+      </c>
+    </row>
+    <row r="87">
+      <c r="A87" s="4" t="n">
+        <v>6</v>
+      </c>
+      <c r="B87" s="5" t="inlineStr">
+        <is>
+          <t>What barriers to HIV &amp; AIDS treatment exist in Bosnia and Herzegovina?</t>
+        </is>
+      </c>
+      <c r="C87" s="4" t="n">
+        <v>11</v>
+      </c>
+      <c r="D87" s="5" t="inlineStr"/>
+      <c r="E87" s="4" t="b">
+        <v>1</v>
+      </c>
+      <c r="F87" s="5" t="inlineStr">
+        <is>
+          <t>Reported number of people receiving ART in Croatia: 1200
+Estimated number of people living with HIV_median in Croatia: 1600.0
+Estimated number of people living with HIV_min in Croatia: 1400.0
+Estimated number of people living with HIV_max in Croatia: 1700.0
+Estimated ART coverage among people living with HIV (%)_median in Croatia: 75.0
+Estimated ART coverage among people living with HIV (%)_min in Croatia: 67.0
+Estimated ART coverage among people living with HIV (%)_max in Croatia: 83.0</t>
+        </is>
+      </c>
+    </row>
+    <row r="88">
+      <c r="A88" s="2" t="n">
+        <v>6</v>
+      </c>
+      <c r="B88" s="3" t="inlineStr">
+        <is>
+          <t>What barriers to HIV &amp; AIDS treatment exist in Bosnia and Herzegovina?</t>
+        </is>
+      </c>
+      <c r="C88" s="2" t="n">
+        <v>12</v>
+      </c>
+      <c r="D88" s="3" t="inlineStr">
+        <is>
+          <t>C:\Users\RAZER\Desktop\portfolio-projects\1. RAG\data\3_txt_KB\HIV_AIDS_data\art_coverage_by_country_clean_Croatia.txt</t>
+        </is>
+      </c>
+      <c r="E88" s="2" t="b">
+        <v>1</v>
+      </c>
+      <c r="F88" s="3" t="inlineStr">
+        <is>
+          <t>Reported number of people receiving ART in Croatia: 1200
+Estimated number of people living with HIV_median in Croatia: 1600.0
+Estimated number of people living with HIV_min in Croatia: 1400.0
+Estimated number of people living with HIV_max in Croatia: 1700.0
+Estimated ART coverage among people living with HIV (%)_median in Croatia: 75.0
+Estimated ART coverage among people living with HIV (%)_min in Croatia: 67.0
+Estimated ART coverage among people living with HIV (%)_max in Croatia: 83.0</t>
+        </is>
+      </c>
+    </row>
+    <row r="89">
+      <c r="A89" s="4" t="n">
+        <v>6</v>
+      </c>
+      <c r="B89" s="5" t="inlineStr">
+        <is>
+          <t>What barriers to HIV &amp; AIDS treatment exist in Bosnia and Herzegovina?</t>
+        </is>
+      </c>
+      <c r="C89" s="4" t="n">
+        <v>13</v>
+      </c>
+      <c r="D89" s="5" t="inlineStr"/>
+      <c r="E89" s="4" t="b">
         <v>0</v>
       </c>
-      <c r="F84" s="3" t="inlineStr">
+      <c r="F89" s="5" t="inlineStr">
         <is>
           <t>Reported number of people receiving ART in Slovakia: 650
 Estimated number of people living with HIV_median in Slovakia: 1200.0
@@ -3139,23 +3247,27 @@
         </is>
       </c>
     </row>
-    <row r="85">
-      <c r="A85" s="4" t="n">
+    <row r="90">
+      <c r="A90" s="2" t="n">
         <v>6</v>
       </c>
-      <c r="B85" s="5" t="inlineStr">
+      <c r="B90" s="3" t="inlineStr">
         <is>
           <t>What barriers to HIV &amp; AIDS treatment exist in Bosnia and Herzegovina?</t>
         </is>
       </c>
-      <c r="C85" s="4" t="n">
-        <v>9</v>
-      </c>
-      <c r="D85" s="5" t="inlineStr"/>
-      <c r="E85" s="4" t="b">
-        <v>1</v>
-      </c>
-      <c r="F85" s="5" t="inlineStr">
+      <c r="C90" s="2" t="n">
+        <v>14</v>
+      </c>
+      <c r="D90" s="3" t="inlineStr">
+        <is>
+          <t>C:\Users\RAZER\Desktop\portfolio-projects\1. RAG\data\3_txt_KB\HIV_AIDS_data\art_coverage_by_country_clean_Slovakia.txt</t>
+        </is>
+      </c>
+      <c r="E90" s="2" t="b">
+        <v>1</v>
+      </c>
+      <c r="F90" s="3" t="inlineStr">
         <is>
           <t>Reported number of people receiving ART in Slovakia: 650
 Estimated number of people living with HIV_median in Slovakia: 1200.0
@@ -3167,27 +3279,27 @@
         </is>
       </c>
     </row>
-    <row r="86">
-      <c r="A86" s="2" t="n">
+    <row r="91">
+      <c r="A91" s="4" t="n">
         <v>6</v>
       </c>
-      <c r="B86" s="3" t="inlineStr">
+      <c r="B91" s="5" t="inlineStr">
         <is>
           <t>What barriers to HIV &amp; AIDS treatment exist in Bosnia and Herzegovina?</t>
         </is>
       </c>
-      <c r="C86" s="2" t="n">
-        <v>10</v>
-      </c>
-      <c r="D86" s="3" t="inlineStr">
+      <c r="C91" s="4" t="n">
+        <v>15</v>
+      </c>
+      <c r="D91" s="5" t="inlineStr">
         <is>
           <t>C:\Users\RAZER\Desktop\portfolio-projects\1. RAG\data\3_txt_KB\HIV_AIDS_data\art_coverage_by_country_clean_Slovakia.txt</t>
         </is>
       </c>
-      <c r="E86" s="2" t="b">
-        <v>1</v>
-      </c>
-      <c r="F86" s="3" t="inlineStr">
+      <c r="E91" s="4" t="b">
+        <v>1</v>
+      </c>
+      <c r="F91" s="5" t="inlineStr">
         <is>
           <t>Reported number of people receiving ART in Slovakia: 650
 Estimated number of people living with HIV_median in Slovakia: 1200.0
@@ -3199,162 +3311,6 @@
         </is>
       </c>
     </row>
-    <row r="87">
-      <c r="A87" s="4" t="n">
-        <v>6</v>
-      </c>
-      <c r="B87" s="5" t="inlineStr">
-        <is>
-          <t>What barriers to HIV &amp; AIDS treatment exist in Bosnia and Herzegovina?</t>
-        </is>
-      </c>
-      <c r="C87" s="4" t="n">
-        <v>11</v>
-      </c>
-      <c r="D87" s="5" t="inlineStr">
-        <is>
-          <t>C:\Users\RAZER\Desktop\portfolio-projects\1. RAG\data\3_txt_KB\HIV_AIDS_data\art_coverage_by_country_clean_Slovakia.txt</t>
-        </is>
-      </c>
-      <c r="E87" s="4" t="b">
-        <v>1</v>
-      </c>
-      <c r="F87" s="5" t="inlineStr">
-        <is>
-          <t>Reported number of people receiving ART in Slovakia: 650
-Estimated number of people living with HIV_median in Slovakia: 1200.0
-Estimated number of people living with HIV_min in Slovakia: 910.0
-Estimated number of people living with HIV_max in Slovakia: 1900.0
-Estimated ART coverage among people living with HIV (%)_median in Slovakia: 54.0
-Estimated ART coverage among people living with HIV (%)_min in Slovakia: 40.0
-Estimated ART coverage among people living with HIV (%)_max in Slovakia: 85.0</t>
-        </is>
-      </c>
-    </row>
-    <row r="88">
-      <c r="A88" s="2" t="n">
-        <v>6</v>
-      </c>
-      <c r="B88" s="3" t="inlineStr">
-        <is>
-          <t>What barriers to HIV &amp; AIDS treatment exist in Bosnia and Herzegovina?</t>
-        </is>
-      </c>
-      <c r="C88" s="2" t="n">
-        <v>12</v>
-      </c>
-      <c r="D88" s="3" t="inlineStr"/>
-      <c r="E88" s="2" t="b">
-        <v>1</v>
-      </c>
-      <c r="F88" s="3" t="inlineStr">
-        <is>
-          <t>Reported number of people receiving ART in Slovakia: 650
-Estimated number of people living with HIV_median in Slovakia: 1200.0
-Estimated number of people living with HIV_min in Slovakia: 910.0
-Estimated number of people living with HIV_max in Slovakia: 1900.0
-Estimated ART coverage among people living with HIV (%)_median in Slovakia: 54.0
-Estimated ART coverage among people living with HIV (%)_min in Slovakia: 40.0
-Estimated ART coverage among people living with HIV (%)_max in Slovakia: 85.0</t>
-        </is>
-      </c>
-    </row>
-    <row r="89">
-      <c r="A89" s="4" t="n">
-        <v>6</v>
-      </c>
-      <c r="B89" s="5" t="inlineStr">
-        <is>
-          <t>What barriers to HIV &amp; AIDS treatment exist in Bosnia and Herzegovina?</t>
-        </is>
-      </c>
-      <c r="C89" s="4" t="n">
-        <v>13</v>
-      </c>
-      <c r="D89" s="5" t="inlineStr">
-        <is>
-          <t>C:\Users\RAZER\Desktop\portfolio-projects\1. RAG\data\3_txt_KB\HIV_AIDS_data\art_coverage_by_country_clean_Slovakia.txt</t>
-        </is>
-      </c>
-      <c r="E89" s="4" t="b">
-        <v>1</v>
-      </c>
-      <c r="F89" s="5" t="inlineStr">
-        <is>
-          <t>Reported number of people receiving ART in Slovakia: 650
-Estimated number of people living with HIV_median in Slovakia: 1200.0
-Estimated number of people living with HIV_min in Slovakia: 910.0
-Estimated number of people living with HIV_max in Slovakia: 1900.0
-Estimated ART coverage among people living with HIV (%)_median in Slovakia: 54.0
-Estimated ART coverage among people living with HIV (%)_min in Slovakia: 40.0
-Estimated ART coverage among people living with HIV (%)_max in Slovakia: 85.0</t>
-        </is>
-      </c>
-    </row>
-    <row r="90">
-      <c r="A90" s="2" t="n">
-        <v>6</v>
-      </c>
-      <c r="B90" s="3" t="inlineStr">
-        <is>
-          <t>What barriers to HIV &amp; AIDS treatment exist in Bosnia and Herzegovina?</t>
-        </is>
-      </c>
-      <c r="C90" s="2" t="n">
-        <v>14</v>
-      </c>
-      <c r="D90" s="3" t="inlineStr">
-        <is>
-          <t>C:\Users\RAZER\Desktop\portfolio-projects\1. RAG\data\3_txt_KB\HIV_AIDS_data\art_coverage_by_country_clean_Slovakia.txt</t>
-        </is>
-      </c>
-      <c r="E90" s="2" t="b">
-        <v>1</v>
-      </c>
-      <c r="F90" s="3" t="inlineStr">
-        <is>
-          <t>Reported number of people receiving ART in Slovakia: 650
-Estimated number of people living with HIV_median in Slovakia: 1200.0
-Estimated number of people living with HIV_min in Slovakia: 910.0
-Estimated number of people living with HIV_max in Slovakia: 1900.0
-Estimated ART coverage among people living with HIV (%)_median in Slovakia: 54.0
-Estimated ART coverage among people living with HIV (%)_min in Slovakia: 40.0
-Estimated ART coverage among people living with HIV (%)_max in Slovakia: 85.0</t>
-        </is>
-      </c>
-    </row>
-    <row r="91">
-      <c r="A91" s="4" t="n">
-        <v>6</v>
-      </c>
-      <c r="B91" s="5" t="inlineStr">
-        <is>
-          <t>What barriers to HIV &amp; AIDS treatment exist in Bosnia and Herzegovina?</t>
-        </is>
-      </c>
-      <c r="C91" s="4" t="n">
-        <v>15</v>
-      </c>
-      <c r="D91" s="5" t="inlineStr">
-        <is>
-          <t>C:\Users\RAZER\Desktop\portfolio-projects\1. RAG\data\3_txt_KB\HIV_AIDS_data\art_coverage_by_country_clean_Bulgaria.txt</t>
-        </is>
-      </c>
-      <c r="E91" s="4" t="b">
-        <v>0</v>
-      </c>
-      <c r="F91" s="5" t="inlineStr">
-        <is>
-          <t>Reported number of people receiving ART in Bulgaria: 1500
-Estimated number of people living with HIV_median in Bulgaria: 3500.0
-Estimated number of people living with HIV_min in Bulgaria: 3000.0
-Estimated number of people living with HIV_max in Bulgaria: 4100.0
-Estimated ART coverage among people living with HIV (%)_median in Bulgaria: 41.0
-Estimated ART coverage among people living with HIV (%)_min in Bulgaria: 35.0
-Estimated ART coverage among people living with HIV (%)_max in Bulgaria: 48.0</t>
-        </is>
-      </c>
-    </row>
     <row r="92">
       <c r="A92" s="2" t="n">
         <v>7</v>
@@ -3367,25 +3323,18 @@
       <c r="C92" s="2" t="n">
         <v>1</v>
       </c>
-      <c r="D92" s="3" t="inlineStr"/>
+      <c r="D92" s="3" t="inlineStr">
+        <is>
+          <t>C:\Users\RAZER\Desktop\portfolio-projects\1. RAG\data\3_txt_KB\UNICEF_Immunization\MCV1_Slovenia.txt</t>
+        </is>
+      </c>
       <c r="E92" s="2" t="b">
         <v>0</v>
       </c>
       <c r="F92" s="3" t="inlineStr">
         <is>
-          <t>MCV1 coverage in Malta (2000): 74.0%
-MCV1 coverage in Malta (2001): 70.0%
-MCV1 coverage in Malta (2002): 65.0%
-MCV1 coverage in Malta (2003): 90.0%
-MCV1 coverage in Malta (2004): 94.0%
-MCV1 coverage in Malta (2005): 86.0%
-MCV1 coverage in Malta (2006): 94.0%
-MCV1 coverage in Malta (2007): 79.0%
-MCV1 coverage in Malta (2008): 78.0%
-MCV1 coverage in Malta (2009): 82.0%
-MCV1 coverage in Malta (2010): 73.0%
-MCV1 coverage in Malta (2011): 84.0%
-MCV1 coverage in Malta (2012): 93.0%</t>
+          <t>MCV1 coverage in Slovenia (2022): 96.0%
+MCV1 coverage in Slovenia (2023): 95.0%</t>
         </is>
       </c>
     </row>
@@ -3407,19 +3356,8 @@
       </c>
       <c r="F93" s="5" t="inlineStr">
         <is>
-          <t>MCV1 coverage in Malta (2000): 74.0%
-MCV1 coverage in Malta (2001): 70.0%
-MCV1 coverage in Malta (2002): 65.0%
-MCV1 coverage in Malta (2003): 90.0%
-MCV1 coverage in Malta (2004): 94.0%
-MCV1 coverage in Malta (2005): 86.0%
-MCV1 coverage in Malta (2006): 94.0%
-MCV1 coverage in Malta (2007): 79.0%
-MCV1 coverage in Malta (2008): 78.0%
-MCV1 coverage in Malta (2009): 82.0%
-MCV1 coverage in Malta (2010): 73.0%
-MCV1 coverage in Malta (2011): 84.0%
-MCV1 coverage in Malta (2012): 93.0%</t>
+          <t>MCV1 coverage in Slovenia (2022): 96.0%
+MCV1 coverage in Slovenia (2023): 95.0%</t>
         </is>
       </c>
     </row>
@@ -3435,29 +3373,14 @@
       <c r="C94" s="2" t="n">
         <v>3</v>
       </c>
-      <c r="D94" s="3" t="inlineStr">
-        <is>
-          <t>C:\Users\RAZER\Desktop\portfolio-projects\1. RAG\data\3_txt_KB\UNICEF_Immunization\MCV1_Malta.txt</t>
-        </is>
-      </c>
+      <c r="D94" s="3" t="inlineStr"/>
       <c r="E94" s="2" t="b">
         <v>1</v>
       </c>
       <c r="F94" s="3" t="inlineStr">
         <is>
-          <t>MCV1 coverage in Malta (2000): 74.0%
-MCV1 coverage in Malta (2001): 70.0%
-MCV1 coverage in Malta (2002): 65.0%
-MCV1 coverage in Malta (2003): 90.0%
-MCV1 coverage in Malta (2004): 94.0%
-MCV1 coverage in Malta (2005): 86.0%
-MCV1 coverage in Malta (2006): 94.0%
-MCV1 coverage in Malta (2007): 79.0%
-MCV1 coverage in Malta (2008): 78.0%
-MCV1 coverage in Malta (2009): 82.0%
-MCV1 coverage in Malta (2010): 73.0%
-MCV1 coverage in Malta (2011): 84.0%
-MCV1 coverage in Malta (2012): 93.0%</t>
+          <t>MCV1 coverage in Slovenia (2022): 96.0%
+MCV1 coverage in Slovenia (2023): 95.0%</t>
         </is>
       </c>
     </row>
@@ -3473,29 +3396,14 @@
       <c r="C95" s="4" t="n">
         <v>4</v>
       </c>
-      <c r="D95" s="5" t="inlineStr">
-        <is>
-          <t>C:\Users\RAZER\Desktop\portfolio-projects\1. RAG\data\3_txt_KB\UNICEF_Immunization\MCV1_Malta.txt</t>
-        </is>
-      </c>
+      <c r="D95" s="5" t="inlineStr"/>
       <c r="E95" s="4" t="b">
         <v>1</v>
       </c>
       <c r="F95" s="5" t="inlineStr">
         <is>
-          <t>MCV1 coverage in Malta (2000): 74.0%
-MCV1 coverage in Malta (2001): 70.0%
-MCV1 coverage in Malta (2002): 65.0%
-MCV1 coverage in Malta (2003): 90.0%
-MCV1 coverage in Malta (2004): 94.0%
-MCV1 coverage in Malta (2005): 86.0%
-MCV1 coverage in Malta (2006): 94.0%
-MCV1 coverage in Malta (2007): 79.0%
-MCV1 coverage in Malta (2008): 78.0%
-MCV1 coverage in Malta (2009): 82.0%
-MCV1 coverage in Malta (2010): 73.0%
-MCV1 coverage in Malta (2011): 84.0%
-MCV1 coverage in Malta (2012): 93.0%</t>
+          <t>MCV1 coverage in Slovenia (2022): 96.0%
+MCV1 coverage in Slovenia (2023): 95.0%</t>
         </is>
       </c>
     </row>
@@ -3513,7 +3421,7 @@
       </c>
       <c r="D96" s="3" t="inlineStr">
         <is>
-          <t>C:\Users\RAZER\Desktop\portfolio-projects\1. RAG\data\3_txt_KB\UNICEF_Immunization\MCV1_Malta.txt</t>
+          <t>C:\Users\RAZER\Desktop\portfolio-projects\1. RAG\data\3_txt_KB\UNICEF_Immunization\MCV1_Slovenia.txt</t>
         </is>
       </c>
       <c r="E96" s="2" t="b">
@@ -3521,19 +3429,8 @@
       </c>
       <c r="F96" s="3" t="inlineStr">
         <is>
-          <t>MCV1 coverage in Malta (2000): 74.0%
-MCV1 coverage in Malta (2001): 70.0%
-MCV1 coverage in Malta (2002): 65.0%
-MCV1 coverage in Malta (2003): 90.0%
-MCV1 coverage in Malta (2004): 94.0%
-MCV1 coverage in Malta (2005): 86.0%
-MCV1 coverage in Malta (2006): 94.0%
-MCV1 coverage in Malta (2007): 79.0%
-MCV1 coverage in Malta (2008): 78.0%
-MCV1 coverage in Malta (2009): 82.0%
-MCV1 coverage in Malta (2010): 73.0%
-MCV1 coverage in Malta (2011): 84.0%
-MCV1 coverage in Malta (2012): 93.0%</t>
+          <t>MCV1 coverage in Slovenia (2022): 96.0%
+MCV1 coverage in Slovenia (2023): 95.0%</t>
         </is>
       </c>
     </row>
@@ -3551,7 +3448,7 @@
       </c>
       <c r="D97" s="5" t="inlineStr">
         <is>
-          <t>C:\Users\RAZER\Desktop\portfolio-projects\1. RAG\data\3_txt_KB\UNICEF_Immunization\MCV1_Malta.txt</t>
+          <t>C:\Users\RAZER\Desktop\portfolio-projects\1. RAG\data\3_txt_KB\UNICEF_Immunization\MCV1_Slovenia.txt</t>
         </is>
       </c>
       <c r="E97" s="4" t="b">
@@ -3559,19 +3456,8 @@
       </c>
       <c r="F97" s="5" t="inlineStr">
         <is>
-          <t>MCV1 coverage in Malta (2000): 74.0%
-MCV1 coverage in Malta (2001): 70.0%
-MCV1 coverage in Malta (2002): 65.0%
-MCV1 coverage in Malta (2003): 90.0%
-MCV1 coverage in Malta (2004): 94.0%
-MCV1 coverage in Malta (2005): 86.0%
-MCV1 coverage in Malta (2006): 94.0%
-MCV1 coverage in Malta (2007): 79.0%
-MCV1 coverage in Malta (2008): 78.0%
-MCV1 coverage in Malta (2009): 82.0%
-MCV1 coverage in Malta (2010): 73.0%
-MCV1 coverage in Malta (2011): 84.0%
-MCV1 coverage in Malta (2012): 93.0%</t>
+          <t>MCV1 coverage in Slovenia (2022): 96.0%
+MCV1 coverage in Slovenia (2023): 95.0%</t>
         </is>
       </c>
     </row>
@@ -3587,21 +3473,18 @@
       <c r="C98" s="2" t="n">
         <v>7</v>
       </c>
-      <c r="D98" s="3" t="inlineStr"/>
+      <c r="D98" s="3" t="inlineStr">
+        <is>
+          <t>C:\Users\RAZER\Desktop\portfolio-projects\1. RAG\data\3_txt_KB\UNICEF_Immunization\MCV1_Slovenia.txt</t>
+        </is>
+      </c>
       <c r="E98" s="2" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="F98" s="3" t="inlineStr">
         <is>
-          <t>MCV2 coverage in Malta (2015): 91.0%
-MCV2 coverage in Malta (2016): 86.0%
-MCV2 coverage in Malta (2017): 83.0%
-MCV2 coverage in Malta (2018): 95.0%
-MCV2 coverage in Malta (2019): 95.0%
-MCV2 coverage in Malta (2020): 99.0%
-MCV2 coverage in Malta (2021): 93.0%
-MCV2 coverage in Malta (2022): 95.0%
-MCV2 coverage in Malta (2023): 95.0%</t>
+          <t>MCV1 coverage in Slovenia (2022): 96.0%
+MCV1 coverage in Slovenia (2023): 95.0%</t>
         </is>
       </c>
     </row>
@@ -3617,21 +3500,18 @@
       <c r="C99" s="4" t="n">
         <v>8</v>
       </c>
-      <c r="D99" s="5" t="inlineStr"/>
+      <c r="D99" s="5" t="inlineStr">
+        <is>
+          <t>C:\Users\RAZER\Desktop\portfolio-projects\1. RAG\data\3_txt_KB\UNICEF_Immunization\MCV1_Slovenia.txt</t>
+        </is>
+      </c>
       <c r="E99" s="4" t="b">
         <v>1</v>
       </c>
       <c r="F99" s="5" t="inlineStr">
         <is>
-          <t>MCV2 coverage in Malta (2015): 91.0%
-MCV2 coverage in Malta (2016): 86.0%
-MCV2 coverage in Malta (2017): 83.0%
-MCV2 coverage in Malta (2018): 95.0%
-MCV2 coverage in Malta (2019): 95.0%
-MCV2 coverage in Malta (2020): 99.0%
-MCV2 coverage in Malta (2021): 93.0%
-MCV2 coverage in Malta (2022): 95.0%
-MCV2 coverage in Malta (2023): 95.0%</t>
+          <t>MCV1 coverage in Slovenia (2022): 96.0%
+MCV1 coverage in Slovenia (2023): 95.0%</t>
         </is>
       </c>
     </row>
@@ -3649,7 +3529,7 @@
       </c>
       <c r="D100" s="3" t="inlineStr">
         <is>
-          <t>C:\Users\RAZER\Desktop\portfolio-projects\1. RAG\data\3_txt_KB\UNICEF_Immunization\MCV2_Malta.txt</t>
+          <t>C:\Users\RAZER\Desktop\portfolio-projects\1. RAG\data\3_txt_KB\UNICEF_Immunization\MCV1_Slovenia.txt</t>
         </is>
       </c>
       <c r="E100" s="2" t="b">
@@ -3657,15 +3537,8 @@
       </c>
       <c r="F100" s="3" t="inlineStr">
         <is>
-          <t>MCV2 coverage in Malta (2015): 91.0%
-MCV2 coverage in Malta (2016): 86.0%
-MCV2 coverage in Malta (2017): 83.0%
-MCV2 coverage in Malta (2018): 95.0%
-MCV2 coverage in Malta (2019): 95.0%
-MCV2 coverage in Malta (2020): 99.0%
-MCV2 coverage in Malta (2021): 93.0%
-MCV2 coverage in Malta (2022): 95.0%
-MCV2 coverage in Malta (2023): 95.0%</t>
+          <t>MCV1 coverage in Slovenia (2022): 96.0%
+MCV1 coverage in Slovenia (2023): 95.0%</t>
         </is>
       </c>
     </row>
@@ -3683,7 +3556,7 @@
       </c>
       <c r="D101" s="5" t="inlineStr">
         <is>
-          <t>C:\Users\RAZER\Desktop\portfolio-projects\1. RAG\data\3_txt_KB\UNICEF_Immunization\MCV2_Malta.txt</t>
+          <t>C:\Users\RAZER\Desktop\portfolio-projects\1. RAG\data\3_txt_KB\UNICEF_Immunization\MCV1_Slovenia.txt</t>
         </is>
       </c>
       <c r="E101" s="4" t="b">
@@ -3691,15 +3564,8 @@
       </c>
       <c r="F101" s="5" t="inlineStr">
         <is>
-          <t>MCV2 coverage in Malta (2015): 91.0%
-MCV2 coverage in Malta (2016): 86.0%
-MCV2 coverage in Malta (2017): 83.0%
-MCV2 coverage in Malta (2018): 95.0%
-MCV2 coverage in Malta (2019): 95.0%
-MCV2 coverage in Malta (2020): 99.0%
-MCV2 coverage in Malta (2021): 93.0%
-MCV2 coverage in Malta (2022): 95.0%
-MCV2 coverage in Malta (2023): 95.0%</t>
+          <t>MCV1 coverage in Slovenia (2022): 96.0%
+MCV1 coverage in Slovenia (2023): 95.0%</t>
         </is>
       </c>
     </row>
@@ -3717,7 +3583,7 @@
       </c>
       <c r="D102" s="3" t="inlineStr">
         <is>
-          <t>C:\Users\RAZER\Desktop\portfolio-projects\1. RAG\data\3_txt_KB\UNICEF_Immunization\MCV2_Malta.txt</t>
+          <t>C:\Users\RAZER\Desktop\portfolio-projects\1. RAG\data\3_txt_KB\UNICEF_Immunization\MCV1_Slovenia.txt</t>
         </is>
       </c>
       <c r="E102" s="2" t="b">
@@ -3725,15 +3591,8 @@
       </c>
       <c r="F102" s="3" t="inlineStr">
         <is>
-          <t>MCV2 coverage in Malta (2015): 91.0%
-MCV2 coverage in Malta (2016): 86.0%
-MCV2 coverage in Malta (2017): 83.0%
-MCV2 coverage in Malta (2018): 95.0%
-MCV2 coverage in Malta (2019): 95.0%
-MCV2 coverage in Malta (2020): 99.0%
-MCV2 coverage in Malta (2021): 93.0%
-MCV2 coverage in Malta (2022): 95.0%
-MCV2 coverage in Malta (2023): 95.0%</t>
+          <t>MCV1 coverage in Slovenia (2022): 96.0%
+MCV1 coverage in Slovenia (2023): 95.0%</t>
         </is>
       </c>
     </row>
@@ -3751,23 +3610,26 @@
       </c>
       <c r="D103" s="5" t="inlineStr">
         <is>
-          <t>C:\Users\RAZER\Desktop\portfolio-projects\1. RAG\data\3_txt_KB\UNICEF_Immunization\MCV2_Malta.txt</t>
+          <t>C:\Users\RAZER\Desktop\portfolio-projects\1. RAG\data\3_txt_KB\UNICEF_Immunization\MCV2_Slovenia.txt</t>
         </is>
       </c>
       <c r="E103" s="4" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="F103" s="5" t="inlineStr">
         <is>
-          <t>MCV2 coverage in Malta (2015): 91.0%
-MCV2 coverage in Malta (2016): 86.0%
-MCV2 coverage in Malta (2017): 83.0%
-MCV2 coverage in Malta (2018): 95.0%
-MCV2 coverage in Malta (2019): 95.0%
-MCV2 coverage in Malta (2020): 99.0%
-MCV2 coverage in Malta (2021): 93.0%
-MCV2 coverage in Malta (2022): 95.0%
-MCV2 coverage in Malta (2023): 95.0%</t>
+          <t>MCV2 coverage in Slovenia (2000): 98.0%
+MCV2 coverage in Slovenia (2001): 98.0%
+MCV2 coverage in Slovenia (2002): 98.0%
+MCV2 coverage in Slovenia (2003): 98.0%
+MCV2 coverage in Slovenia (2004): 99.0%
+MCV2 coverage in Slovenia (2005): 99.0%
+MCV2 coverage in Slovenia (2006): 99.0%
+MCV2 coverage in Slovenia (2007): 98.0%
+MCV2 coverage in Slovenia (2008): 98.0%
+MCV2 coverage in Slovenia (2009): 98.0%
+MCV2 coverage in Slovenia (2010): 96.0%
+MCV2 coverage in Slovenia (2011): 96.0%</t>
         </is>
       </c>
     </row>
@@ -3783,24 +3645,28 @@
       <c r="C104" s="2" t="n">
         <v>13</v>
       </c>
-      <c r="D104" s="3" t="inlineStr"/>
+      <c r="D104" s="3" t="inlineStr">
+        <is>
+          <t>C:\Users\RAZER\Desktop\portfolio-projects\1. RAG\data\3_txt_KB\UNICEF_Immunization\MCV2_Slovenia.txt</t>
+        </is>
+      </c>
       <c r="E104" s="2" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="F104" s="3" t="inlineStr">
         <is>
-          <t>MCV1 coverage in Malta (2012): 93.0%
-MCV1 coverage in Malta (2013): 99.0%
-MCV1 coverage in Malta (2014): 98.0%
-MCV1 coverage in Malta (2015): 89.0%
-MCV1 coverage in Malta (2016): 93.0%
-MCV1 coverage in Malta (2017): 91.0%
-MCV1 coverage in Malta (2018): 96.0%
-MCV1 coverage in Malta (2019): 96.0%
-MCV1 coverage in Malta (2020): 95.0%
-MCV1 coverage in Malta (2021): 90.0%
-MCV1 coverage in Malta (2022): 96.0%
-MCV1 coverage in Malta (2023): 95.0%</t>
+          <t>MCV2 coverage in Slovenia (2000): 98.0%
+MCV2 coverage in Slovenia (2001): 98.0%
+MCV2 coverage in Slovenia (2002): 98.0%
+MCV2 coverage in Slovenia (2003): 98.0%
+MCV2 coverage in Slovenia (2004): 99.0%
+MCV2 coverage in Slovenia (2005): 99.0%
+MCV2 coverage in Slovenia (2006): 99.0%
+MCV2 coverage in Slovenia (2007): 98.0%
+MCV2 coverage in Slovenia (2008): 98.0%
+MCV2 coverage in Slovenia (2009): 98.0%
+MCV2 coverage in Slovenia (2010): 96.0%
+MCV2 coverage in Slovenia (2011): 96.0%</t>
         </is>
       </c>
     </row>
@@ -3818,7 +3684,7 @@
       </c>
       <c r="D105" s="5" t="inlineStr">
         <is>
-          <t>C:\Users\RAZER\Desktop\portfolio-projects\1. RAG\data\3_txt_KB\UNICEF_Immunization\MCV1_Malta.txt</t>
+          <t>C:\Users\RAZER\Desktop\portfolio-projects\1. RAG\data\3_txt_KB\UNICEF_Immunization\MCV2_Slovenia.txt</t>
         </is>
       </c>
       <c r="E105" s="4" t="b">
@@ -3826,18 +3692,18 @@
       </c>
       <c r="F105" s="5" t="inlineStr">
         <is>
-          <t>MCV1 coverage in Malta (2012): 93.0%
-MCV1 coverage in Malta (2013): 99.0%
-MCV1 coverage in Malta (2014): 98.0%
-MCV1 coverage in Malta (2015): 89.0%
-MCV1 coverage in Malta (2016): 93.0%
-MCV1 coverage in Malta (2017): 91.0%
-MCV1 coverage in Malta (2018): 96.0%
-MCV1 coverage in Malta (2019): 96.0%
-MCV1 coverage in Malta (2020): 95.0%
-MCV1 coverage in Malta (2021): 90.0%
-MCV1 coverage in Malta (2022): 96.0%
-MCV1 coverage in Malta (2023): 95.0%</t>
+          <t>MCV2 coverage in Slovenia (2000): 98.0%
+MCV2 coverage in Slovenia (2001): 98.0%
+MCV2 coverage in Slovenia (2002): 98.0%
+MCV2 coverage in Slovenia (2003): 98.0%
+MCV2 coverage in Slovenia (2004): 99.0%
+MCV2 coverage in Slovenia (2005): 99.0%
+MCV2 coverage in Slovenia (2006): 99.0%
+MCV2 coverage in Slovenia (2007): 98.0%
+MCV2 coverage in Slovenia (2008): 98.0%
+MCV2 coverage in Slovenia (2009): 98.0%
+MCV2 coverage in Slovenia (2010): 96.0%
+MCV2 coverage in Slovenia (2011): 96.0%</t>
         </is>
       </c>
     </row>
@@ -3855,7 +3721,7 @@
       </c>
       <c r="D106" s="3" t="inlineStr">
         <is>
-          <t>C:\Users\RAZER\Desktop\portfolio-projects\1. RAG\data\3_txt_KB\UNICEF_Immunization\MCV1_Malta.txt</t>
+          <t>C:\Users\RAZER\Desktop\portfolio-projects\1. RAG\data\3_txt_KB\UNICEF_Immunization\MCV2_Slovenia.txt</t>
         </is>
       </c>
       <c r="E106" s="2" t="b">
@@ -3863,18 +3729,18 @@
       </c>
       <c r="F106" s="3" t="inlineStr">
         <is>
-          <t>MCV1 coverage in Malta (2012): 93.0%
-MCV1 coverage in Malta (2013): 99.0%
-MCV1 coverage in Malta (2014): 98.0%
-MCV1 coverage in Malta (2015): 89.0%
-MCV1 coverage in Malta (2016): 93.0%
-MCV1 coverage in Malta (2017): 91.0%
-MCV1 coverage in Malta (2018): 96.0%
-MCV1 coverage in Malta (2019): 96.0%
-MCV1 coverage in Malta (2020): 95.0%
-MCV1 coverage in Malta (2021): 90.0%
-MCV1 coverage in Malta (2022): 96.0%
-MCV1 coverage in Malta (2023): 95.0%</t>
+          <t>MCV2 coverage in Slovenia (2000): 98.0%
+MCV2 coverage in Slovenia (2001): 98.0%
+MCV2 coverage in Slovenia (2002): 98.0%
+MCV2 coverage in Slovenia (2003): 98.0%
+MCV2 coverage in Slovenia (2004): 99.0%
+MCV2 coverage in Slovenia (2005): 99.0%
+MCV2 coverage in Slovenia (2006): 99.0%
+MCV2 coverage in Slovenia (2007): 98.0%
+MCV2 coverage in Slovenia (2008): 98.0%
+MCV2 coverage in Slovenia (2009): 98.0%
+MCV2 coverage in Slovenia (2010): 96.0%
+MCV2 coverage in Slovenia (2011): 96.0%</t>
         </is>
       </c>
     </row>
@@ -3890,25 +3756,23 @@
       <c r="C107" s="4" t="n">
         <v>1</v>
       </c>
-      <c r="D107" s="5" t="inlineStr"/>
+      <c r="D107" s="5" t="inlineStr">
+        <is>
+          <t>C:\Users\RAZER\Desktop\portfolio-projects\1. RAG\data\3_txt_KB\HIV_AIDS_data\art_coverage_by_country_clean_Denmark.txt</t>
+        </is>
+      </c>
       <c r="E107" s="4" t="b">
         <v>0</v>
       </c>
       <c r="F107" s="5" t="inlineStr">
         <is>
-          <t>DTP3 coverage in Italy (2000): 87.0%
-DTP3 coverage in Italy (2001): 93.0%
-DTP3 coverage in Italy (2002): 93.0%
-DTP3 coverage in Italy (2003): 96.0%
-DTP3 coverage in Italy (2004): 94.0%
-DTP3 coverage in Italy (2005): 95.0%
-DTP3 coverage in Italy (2006): 96.0%
-DTP3 coverage in Italy (2007): 97.0%
-DTP3 coverage in Italy (2008): 96.0%
-DTP3 coverage in Italy (2009): 96.0%
-DTP3 coverage in Italy (2010): 96.0%
-DTP3 coverage in Italy (2011): 96.0%
-DTP3 coverage in Italy (2012): 97.0%</t>
+          <t>Reported number of people receiving ART in Denmark: 5500
+Estimated number of people living with HIV_median in Denmark: 6200.0
+Estimated number of people living with HIV_min in Denmark: 5600.0
+Estimated number of people living with HIV_max in Denmark: 7000.0
+Estimated ART coverage among people living with HIV (%)_median in Denmark: 89.0
+Estimated ART coverage among people living with HIV (%)_min in Denmark: 79.0
+Estimated ART coverage among people living with HIV (%)_max in Denmark: 95.0</t>
         </is>
       </c>
     </row>
@@ -3926,7 +3790,7 @@
       </c>
       <c r="D108" s="3" t="inlineStr">
         <is>
-          <t>C:\Users\RAZER\Desktop\portfolio-projects\1. RAG\data\3_txt_KB\UNICEF_Immunization\DTP3_Italy.txt</t>
+          <t>C:\Users\RAZER\Desktop\portfolio-projects\1. RAG\data\3_txt_KB\HIV_AIDS_data\art_coverage_by_country_clean_Denmark.txt</t>
         </is>
       </c>
       <c r="E108" s="2" t="b">
@@ -3934,19 +3798,13 @@
       </c>
       <c r="F108" s="3" t="inlineStr">
         <is>
-          <t>DTP3 coverage in Italy (2000): 87.0%
-DTP3 coverage in Italy (2001): 93.0%
-DTP3 coverage in Italy (2002): 93.0%
-DTP3 coverage in Italy (2003): 96.0%
-DTP3 coverage in Italy (2004): 94.0%
-DTP3 coverage in Italy (2005): 95.0%
-DTP3 coverage in Italy (2006): 96.0%
-DTP3 coverage in Italy (2007): 97.0%
-DTP3 coverage in Italy (2008): 96.0%
-DTP3 coverage in Italy (2009): 96.0%
-DTP3 coverage in Italy (2010): 96.0%
-DTP3 coverage in Italy (2011): 96.0%
-DTP3 coverage in Italy (2012): 97.0%</t>
+          <t>Reported number of people receiving ART in Denmark: 5500
+Estimated number of people living with HIV_median in Denmark: 6200.0
+Estimated number of people living with HIV_min in Denmark: 5600.0
+Estimated number of people living with HIV_max in Denmark: 7000.0
+Estimated ART coverage among people living with HIV (%)_median in Denmark: 89.0
+Estimated ART coverage among people living with HIV (%)_min in Denmark: 79.0
+Estimated ART coverage among people living with HIV (%)_max in Denmark: 95.0</t>
         </is>
       </c>
     </row>
@@ -3964,7 +3822,7 @@
       </c>
       <c r="D109" s="5" t="inlineStr">
         <is>
-          <t>C:\Users\RAZER\Desktop\portfolio-projects\1. RAG\data\3_txt_KB\UNICEF_Immunization\DTP3_Italy.txt</t>
+          <t>C:\Users\RAZER\Desktop\portfolio-projects\1. RAG\data\3_txt_KB\HIV_AIDS_data\art_coverage_by_country_clean_Denmark.txt</t>
         </is>
       </c>
       <c r="E109" s="4" t="b">
@@ -3972,19 +3830,13 @@
       </c>
       <c r="F109" s="5" t="inlineStr">
         <is>
-          <t>DTP3 coverage in Italy (2000): 87.0%
-DTP3 coverage in Italy (2001): 93.0%
-DTP3 coverage in Italy (2002): 93.0%
-DTP3 coverage in Italy (2003): 96.0%
-DTP3 coverage in Italy (2004): 94.0%
-DTP3 coverage in Italy (2005): 95.0%
-DTP3 coverage in Italy (2006): 96.0%
-DTP3 coverage in Italy (2007): 97.0%
-DTP3 coverage in Italy (2008): 96.0%
-DTP3 coverage in Italy (2009): 96.0%
-DTP3 coverage in Italy (2010): 96.0%
-DTP3 coverage in Italy (2011): 96.0%
-DTP3 coverage in Italy (2012): 97.0%</t>
+          <t>Reported number of people receiving ART in Denmark: 5500
+Estimated number of people living with HIV_median in Denmark: 6200.0
+Estimated number of people living with HIV_min in Denmark: 5600.0
+Estimated number of people living with HIV_max in Denmark: 7000.0
+Estimated ART coverage among people living with HIV (%)_median in Denmark: 89.0
+Estimated ART coverage among people living with HIV (%)_min in Denmark: 79.0
+Estimated ART coverage among people living with HIV (%)_max in Denmark: 95.0</t>
         </is>
       </c>
     </row>
@@ -4002,7 +3854,7 @@
       </c>
       <c r="D110" s="3" t="inlineStr">
         <is>
-          <t>C:\Users\RAZER\Desktop\portfolio-projects\1. RAG\data\3_txt_KB\UNICEF_Immunization\DTP3_Italy.txt</t>
+          <t>C:\Users\RAZER\Desktop\portfolio-projects\1. RAG\data\3_txt_KB\HIV_AIDS_data\art_coverage_by_country_clean_Denmark.txt</t>
         </is>
       </c>
       <c r="E110" s="2" t="b">
@@ -4010,19 +3862,13 @@
       </c>
       <c r="F110" s="3" t="inlineStr">
         <is>
-          <t>DTP3 coverage in Italy (2000): 87.0%
-DTP3 coverage in Italy (2001): 93.0%
-DTP3 coverage in Italy (2002): 93.0%
-DTP3 coverage in Italy (2003): 96.0%
-DTP3 coverage in Italy (2004): 94.0%
-DTP3 coverage in Italy (2005): 95.0%
-DTP3 coverage in Italy (2006): 96.0%
-DTP3 coverage in Italy (2007): 97.0%
-DTP3 coverage in Italy (2008): 96.0%
-DTP3 coverage in Italy (2009): 96.0%
-DTP3 coverage in Italy (2010): 96.0%
-DTP3 coverage in Italy (2011): 96.0%
-DTP3 coverage in Italy (2012): 97.0%</t>
+          <t>Reported number of people receiving ART in Denmark: 5500
+Estimated number of people living with HIV_median in Denmark: 6200.0
+Estimated number of people living with HIV_min in Denmark: 5600.0
+Estimated number of people living with HIV_max in Denmark: 7000.0
+Estimated ART coverage among people living with HIV (%)_median in Denmark: 89.0
+Estimated ART coverage among people living with HIV (%)_min in Denmark: 79.0
+Estimated ART coverage among people living with HIV (%)_max in Denmark: 95.0</t>
         </is>
       </c>
     </row>
@@ -4038,29 +3884,13 @@
       <c r="C111" s="4" t="n">
         <v>5</v>
       </c>
-      <c r="D111" s="5" t="inlineStr">
-        <is>
-          <t>C:\Users\RAZER\Desktop\portfolio-projects\1. RAG\data\3_txt_KB\UNICEF_Immunization\DTP3_Italy.txt</t>
-        </is>
-      </c>
+      <c r="D111" s="5" t="inlineStr"/>
       <c r="E111" s="4" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="F111" s="5" t="inlineStr">
         <is>
-          <t>DTP3 coverage in Italy (2000): 87.0%
-DTP3 coverage in Italy (2001): 93.0%
-DTP3 coverage in Italy (2002): 93.0%
-DTP3 coverage in Italy (2003): 96.0%
-DTP3 coverage in Italy (2004): 94.0%
-DTP3 coverage in Italy (2005): 95.0%
-DTP3 coverage in Italy (2006): 96.0%
-DTP3 coverage in Italy (2007): 97.0%
-DTP3 coverage in Italy (2008): 96.0%
-DTP3 coverage in Italy (2009): 96.0%
-DTP3 coverage in Italy (2010): 96.0%
-DTP3 coverage in Italy (2011): 96.0%
-DTP3 coverage in Italy (2012): 97.0%</t>
+          <t>Question b1_i — In your opinion, how widespread are positive measures to promote respect for the human rights of transgender people in the country where you live? * | Denmark responses (Transgender): Very widespread: 1%, Fairly widespread: 11%, Fairly rare: 27%, Very rare: 52%, Don`t know: 9%</t>
         </is>
       </c>
     </row>
@@ -4076,28 +3906,13 @@
       <c r="C112" s="2" t="n">
         <v>6</v>
       </c>
-      <c r="D112" s="3" t="inlineStr">
-        <is>
-          <t>C:\Users\RAZER\Desktop\portfolio-projects\1. RAG\data\3_txt_KB\UNICEF_Immunization\DTP3_Italy.txt</t>
-        </is>
-      </c>
+      <c r="D112" s="3" t="inlineStr"/>
       <c r="E112" s="2" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="F112" s="3" t="inlineStr">
         <is>
-          <t>DTP3 coverage in Italy (2012): 97.0%
-DTP3 coverage in Italy (2013): 96.0%
-DTP3 coverage in Italy (2014): 95.0%
-DTP3 coverage in Italy (2015): 93.0%
-DTP3 coverage in Italy (2016): 94.0%
-DTP3 coverage in Italy (2017): 95.0%
-DTP3 coverage in Italy (2018): 95.0%
-DTP3 coverage in Italy (2019): 96.0%
-DTP3 coverage in Italy (2020): 94.0%
-DTP3 coverage in Italy (2021): 94.0%
-DTP3 coverage in Italy (2022): 95.0%
-DTP3 coverage in Italy (2023): 95.0%</t>
+          <t>Question b1_i — In your opinion, how widespread are positive measures to promote respect for the human rights of transgender people in the country where you live? * | Denmark responses (Transgender): Very widespread: 1%, Fairly widespread: 11%, Fairly rare: 27%, Very rare: 52%, Don`t know: 9%</t>
         </is>
       </c>
     </row>
@@ -4113,24 +3928,17 @@
       <c r="C113" s="4" t="n">
         <v>7</v>
       </c>
-      <c r="D113" s="5" t="inlineStr"/>
+      <c r="D113" s="5" t="inlineStr">
+        <is>
+          <t>C:\Users\RAZER\Desktop\portfolio-projects\1. RAG\data\3_txt_KB\LGBT_EU\by_country\LGBT_Survey_DailyLife\b1_i_answer_by_Denmark.txt</t>
+        </is>
+      </c>
       <c r="E113" s="4" t="b">
         <v>1</v>
       </c>
       <c r="F113" s="5" t="inlineStr">
         <is>
-          <t>DTP3 coverage in Italy (2012): 97.0%
-DTP3 coverage in Italy (2013): 96.0%
-DTP3 coverage in Italy (2014): 95.0%
-DTP3 coverage in Italy (2015): 93.0%
-DTP3 coverage in Italy (2016): 94.0%
-DTP3 coverage in Italy (2017): 95.0%
-DTP3 coverage in Italy (2018): 95.0%
-DTP3 coverage in Italy (2019): 96.0%
-DTP3 coverage in Italy (2020): 94.0%
-DTP3 coverage in Italy (2021): 94.0%
-DTP3 coverage in Italy (2022): 95.0%
-DTP3 coverage in Italy (2023): 95.0%</t>
+          <t>Question b1_i — In your opinion, how widespread are positive measures to promote respect for the human rights of transgender people in the country where you live? * | Denmark responses (Transgender): Very widespread: 1%, Fairly widespread: 11%, Fairly rare: 27%, Very rare: 52%, Don`t know: 9%</t>
         </is>
       </c>
     </row>
@@ -4148,7 +3956,7 @@
       </c>
       <c r="D114" s="3" t="inlineStr">
         <is>
-          <t>C:\Users\RAZER\Desktop\portfolio-projects\1. RAG\data\3_txt_KB\UNICEF_Immunization\DTP3_Italy.txt</t>
+          <t>C:\Users\RAZER\Desktop\portfolio-projects\1. RAG\data\3_txt_KB\LGBT_EU\by_country\LGBT_Survey_DailyLife\b1_i_answer_by_Denmark.txt</t>
         </is>
       </c>
       <c r="E114" s="2" t="b">
@@ -4156,18 +3964,7 @@
       </c>
       <c r="F114" s="3" t="inlineStr">
         <is>
-          <t>DTP3 coverage in Italy (2012): 97.0%
-DTP3 coverage in Italy (2013): 96.0%
-DTP3 coverage in Italy (2014): 95.0%
-DTP3 coverage in Italy (2015): 93.0%
-DTP3 coverage in Italy (2016): 94.0%
-DTP3 coverage in Italy (2017): 95.0%
-DTP3 coverage in Italy (2018): 95.0%
-DTP3 coverage in Italy (2019): 96.0%
-DTP3 coverage in Italy (2020): 94.0%
-DTP3 coverage in Italy (2021): 94.0%
-DTP3 coverage in Italy (2022): 95.0%
-DTP3 coverage in Italy (2023): 95.0%</t>
+          <t>Question b1_i — In your opinion, how widespread are positive measures to promote respect for the human rights of transgender people in the country where you live? * | Denmark responses (Transgender): Very widespread: 1%, Fairly widespread: 11%, Fairly rare: 27%, Very rare: 52%, Don`t know: 9%</t>
         </is>
       </c>
     </row>
@@ -4185,7 +3982,7 @@
       </c>
       <c r="D115" s="5" t="inlineStr">
         <is>
-          <t>C:\Users\RAZER\Desktop\portfolio-projects\1. RAG\data\3_txt_KB\UNICEF_Immunization\DTP3_Italy.txt</t>
+          <t>C:\Users\RAZER\Desktop\portfolio-projects\1. RAG\data\3_txt_KB\LGBT_EU\by_country\LGBT_Survey_DailyLife\b1_i_answer_by_Denmark.txt</t>
         </is>
       </c>
       <c r="E115" s="4" t="b">
@@ -4193,18 +3990,7 @@
       </c>
       <c r="F115" s="5" t="inlineStr">
         <is>
-          <t>DTP3 coverage in Italy (2012): 97.0%
-DTP3 coverage in Italy (2013): 96.0%
-DTP3 coverage in Italy (2014): 95.0%
-DTP3 coverage in Italy (2015): 93.0%
-DTP3 coverage in Italy (2016): 94.0%
-DTP3 coverage in Italy (2017): 95.0%
-DTP3 coverage in Italy (2018): 95.0%
-DTP3 coverage in Italy (2019): 96.0%
-DTP3 coverage in Italy (2020): 94.0%
-DTP3 coverage in Italy (2021): 94.0%
-DTP3 coverage in Italy (2022): 95.0%
-DTP3 coverage in Italy (2023): 95.0%</t>
+          <t>Question b1_i — In your opinion, how widespread are positive measures to promote respect for the human rights of transgender people in the country where you live? * | Denmark responses (Transgender): Very widespread: 1%, Fairly widespread: 11%, Fairly rare: 27%, Very rare: 52%, Don`t know: 9%</t>
         </is>
       </c>
     </row>
@@ -4222,7 +4008,7 @@
       </c>
       <c r="D116" s="3" t="inlineStr">
         <is>
-          <t>C:\Users\RAZER\Desktop\portfolio-projects\1. RAG\data\3_txt_KB\UNICEF_Immunization\DTP3_Italy.txt</t>
+          <t>C:\Users\RAZER\Desktop\portfolio-projects\1. RAG\data\3_txt_KB\LGBT_EU\by_country\LGBT_Survey_DailyLife\b1_i_answer_by_Denmark.txt</t>
         </is>
       </c>
       <c r="E116" s="2" t="b">
@@ -4230,18 +4016,7 @@
       </c>
       <c r="F116" s="3" t="inlineStr">
         <is>
-          <t>DTP3 coverage in Italy (2012): 97.0%
-DTP3 coverage in Italy (2013): 96.0%
-DTP3 coverage in Italy (2014): 95.0%
-DTP3 coverage in Italy (2015): 93.0%
-DTP3 coverage in Italy (2016): 94.0%
-DTP3 coverage in Italy (2017): 95.0%
-DTP3 coverage in Italy (2018): 95.0%
-DTP3 coverage in Italy (2019): 96.0%
-DTP3 coverage in Italy (2020): 94.0%
-DTP3 coverage in Italy (2021): 94.0%
-DTP3 coverage in Italy (2022): 95.0%
-DTP3 coverage in Italy (2023): 95.0%</t>
+          <t>Question b1_i — In your opinion, how widespread are positive measures to promote respect for the human rights of transgender people in the country where you live? * | Denmark responses (Transgender): Very widespread: 1%, Fairly widespread: 11%, Fairly rare: 27%, Very rare: 52%, Don`t know: 9%</t>
         </is>
       </c>
     </row>
@@ -4257,25 +4032,17 @@
       <c r="C117" s="4" t="n">
         <v>11</v>
       </c>
-      <c r="D117" s="5" t="inlineStr"/>
+      <c r="D117" s="5" t="inlineStr">
+        <is>
+          <t>C:\Users\RAZER\Desktop\portfolio-projects\1. RAG\data\3_txt_KB\LGBT_EU\by_country\LGBT_Survey_DailyLife\b1_i_answer_by_Denmark.txt</t>
+        </is>
+      </c>
       <c r="E117" s="4" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="F117" s="5" t="inlineStr">
         <is>
-          <t>DTP3 coverage in Greece (2000): 89.0%
-DTP3 coverage in Greece (2001): 91.0%
-DTP3 coverage in Greece (2002): 92.0%
-DTP3 coverage in Greece (2003): 94.0%
-DTP3 coverage in Greece (2004): 95.0%
-DTP3 coverage in Greece (2005): 96.0%
-DTP3 coverage in Greece (2006): 98.0%
-DTP3 coverage in Greece (2007): 99.0%
-DTP3 coverage in Greece (2008): 99.0%
-DTP3 coverage in Greece (2009): 99.0%
-DTP3 coverage in Greece (2010): 99.0%
-DTP3 coverage in Greece (2011): 99.0%
-DTP3 coverage in Greece (2012): 99.0%</t>
+          <t>Question b1_i — In your opinion, how widespread are positive measures to promote respect for the human rights of transgender people in the country where you live? * | Denmark responses (Transgender): Very widespread: 1%, Fairly widespread: 11%, Fairly rare: 27%, Very rare: 52%, Don`t know: 9%</t>
         </is>
       </c>
     </row>
@@ -4293,7 +4060,7 @@
       </c>
       <c r="D118" s="3" t="inlineStr">
         <is>
-          <t>C:\Users\RAZER\Desktop\portfolio-projects\1. RAG\data\3_txt_KB\UNICEF_Immunization\DTP3_Greece.txt</t>
+          <t>C:\Users\RAZER\Desktop\portfolio-projects\1. RAG\data\3_txt_KB\LGBT_EU\by_country\LGBT_Survey_DailyLife\b1_i_answer_by_Denmark.txt</t>
         </is>
       </c>
       <c r="E118" s="2" t="b">
@@ -4301,19 +4068,7 @@
       </c>
       <c r="F118" s="3" t="inlineStr">
         <is>
-          <t>DTP3 coverage in Greece (2000): 89.0%
-DTP3 coverage in Greece (2001): 91.0%
-DTP3 coverage in Greece (2002): 92.0%
-DTP3 coverage in Greece (2003): 94.0%
-DTP3 coverage in Greece (2004): 95.0%
-DTP3 coverage in Greece (2005): 96.0%
-DTP3 coverage in Greece (2006): 98.0%
-DTP3 coverage in Greece (2007): 99.0%
-DTP3 coverage in Greece (2008): 99.0%
-DTP3 coverage in Greece (2009): 99.0%
-DTP3 coverage in Greece (2010): 99.0%
-DTP3 coverage in Greece (2011): 99.0%
-DTP3 coverage in Greece (2012): 99.0%</t>
+          <t>Question b1_i — In your opinion, how widespread are positive measures to promote respect for the human rights of transgender people in the country where you live? * | Denmark responses (Transgender): Very widespread: 1%, Fairly widespread: 11%, Fairly rare: 27%, Very rare: 52%, Don`t know: 9%</t>
         </is>
       </c>
     </row>
@@ -4331,7 +4086,7 @@
       </c>
       <c r="D119" s="5" t="inlineStr">
         <is>
-          <t>C:\Users\RAZER\Desktop\portfolio-projects\1. RAG\data\3_txt_KB\UNICEF_Immunization\DTP3_Greece.txt</t>
+          <t>C:\Users\RAZER\Desktop\portfolio-projects\1. RAG\data\3_txt_KB\LGBT_EU\by_country\LGBT_Survey_DailyLife\b1_i_answer_by_Denmark.txt</t>
         </is>
       </c>
       <c r="E119" s="4" t="b">
@@ -4339,19 +4094,7 @@
       </c>
       <c r="F119" s="5" t="inlineStr">
         <is>
-          <t>DTP3 coverage in Greece (2000): 89.0%
-DTP3 coverage in Greece (2001): 91.0%
-DTP3 coverage in Greece (2002): 92.0%
-DTP3 coverage in Greece (2003): 94.0%
-DTP3 coverage in Greece (2004): 95.0%
-DTP3 coverage in Greece (2005): 96.0%
-DTP3 coverage in Greece (2006): 98.0%
-DTP3 coverage in Greece (2007): 99.0%
-DTP3 coverage in Greece (2008): 99.0%
-DTP3 coverage in Greece (2009): 99.0%
-DTP3 coverage in Greece (2010): 99.0%
-DTP3 coverage in Greece (2011): 99.0%
-DTP3 coverage in Greece (2012): 99.0%</t>
+          <t>Question b1_i — In your opinion, how widespread are positive measures to promote respect for the human rights of transgender people in the country where you live? * | Denmark responses (Transgender): Very widespread: 1%, Fairly widespread: 11%, Fairly rare: 27%, Very rare: 52%, Don`t know: 9%</t>
         </is>
       </c>
     </row>
@@ -4367,29 +4110,13 @@
       <c r="C120" s="2" t="n">
         <v>14</v>
       </c>
-      <c r="D120" s="3" t="inlineStr">
-        <is>
-          <t>C:\Users\RAZER\Desktop\portfolio-projects\1. RAG\data\3_txt_KB\UNICEF_Immunization\DTP3_Greece.txt</t>
-        </is>
-      </c>
+      <c r="D120" s="3" t="inlineStr"/>
       <c r="E120" s="2" t="b">
         <v>1</v>
       </c>
       <c r="F120" s="3" t="inlineStr">
         <is>
-          <t>DTP3 coverage in Greece (2000): 89.0%
-DTP3 coverage in Greece (2001): 91.0%
-DTP3 coverage in Greece (2002): 92.0%
-DTP3 coverage in Greece (2003): 94.0%
-DTP3 coverage in Greece (2004): 95.0%
-DTP3 coverage in Greece (2005): 96.0%
-DTP3 coverage in Greece (2006): 98.0%
-DTP3 coverage in Greece (2007): 99.0%
-DTP3 coverage in Greece (2008): 99.0%
-DTP3 coverage in Greece (2009): 99.0%
-DTP3 coverage in Greece (2010): 99.0%
-DTP3 coverage in Greece (2011): 99.0%
-DTP3 coverage in Greece (2012): 99.0%</t>
+          <t>Question b1_i — In your opinion, how widespread are positive measures to promote respect for the human rights of transgender people in the country where you live? * | Denmark responses (Transgender): Very widespread: 1%, Fairly widespread: 11%, Fairly rare: 27%, Very rare: 52%, Don`t know: 9%</t>
         </is>
       </c>
     </row>
@@ -4407,7 +4134,7 @@
       </c>
       <c r="D121" s="5" t="inlineStr">
         <is>
-          <t>C:\Users\RAZER\Desktop\portfolio-projects\1. RAG\data\3_txt_KB\UNICEF_Immunization\DTP3_Greece.txt</t>
+          <t>C:\Users\RAZER\Desktop\portfolio-projects\1. RAG\data\3_txt_KB\LGBT_EU\by_country\LGBT_Survey_DailyLife\b1_i_answer_by_Denmark.txt</t>
         </is>
       </c>
       <c r="E121" s="4" t="b">
@@ -4415,19 +4142,7 @@
       </c>
       <c r="F121" s="5" t="inlineStr">
         <is>
-          <t>DTP3 coverage in Greece (2000): 89.0%
-DTP3 coverage in Greece (2001): 91.0%
-DTP3 coverage in Greece (2002): 92.0%
-DTP3 coverage in Greece (2003): 94.0%
-DTP3 coverage in Greece (2004): 95.0%
-DTP3 coverage in Greece (2005): 96.0%
-DTP3 coverage in Greece (2006): 98.0%
-DTP3 coverage in Greece (2007): 99.0%
-DTP3 coverage in Greece (2008): 99.0%
-DTP3 coverage in Greece (2009): 99.0%
-DTP3 coverage in Greece (2010): 99.0%
-DTP3 coverage in Greece (2011): 99.0%
-DTP3 coverage in Greece (2012): 99.0%</t>
+          <t>Question b1_i — In your opinion, how widespread are positive measures to promote respect for the human rights of transgender people in the country where you live? * | Denmark responses (Transgender): Very widespread: 1%, Fairly widespread: 11%, Fairly rare: 27%, Very rare: 52%, Don`t know: 9%</t>
         </is>
       </c>
     </row>
